--- a/workspaces/btc_daily_14days/roc/roc_14.xlsx
+++ b/workspaces/btc_daily_14days/roc/roc_14.xlsx
@@ -575,46 +575,46 @@
         <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.352715525943871</v>
+        <v>1.347801500660303</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-7.95311543200156</v>
+        <v>-7.927769947260316</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.042099118256054</v>
+        <v>7.019230691089255</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>18.72126243284465</v>
+        <v>18.66073935947623</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.787173170737624</v>
+        <v>2.777702018568441</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.7652890861556827</v>
+        <v>-0.7631151018951243</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.70508235920762</v>
+        <v>10.67083282704066</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-9.024339039542163</v>
+        <v>-8.99525378145696</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.38042811842223</v>
+        <v>-1.375458579465771</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.47644650027177</v>
+        <v>5.459641929526136</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.272411714886921</v>
+        <v>5.256353500599104</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9.164846405555721</v>
+        <v>9.136187125915882</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.88792088580756</v>
+        <v>4.873043364009362</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.998176087130986</v>
+        <v>8.970062967190785</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>40</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.00656167979002</v>
+        <v>9.973630687616719</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>15.89892949134373</v>
+        <v>15.84769097260568</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>13.00665752498878</v>
+        <v>12.96415945404453</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.634819237566553</v>
+        <v>5.615550010409443</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>17.60963632269608</v>
+        <v>17.55215992666621</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.396193578131971</v>
+        <v>5.378512635234102</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.808961279773236</v>
+        <v>2.79964075304585</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9.854374366711049</v>
+        <v>9.822991870326227</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7.290593683468252</v>
+        <v>7.267652794351854</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.945929632235604</v>
+        <v>8.917649426428099</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>16.26144100236816</v>
+        <v>16.20964471435941</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>16.30011890473102</v>
+        <v>16.24795576242778</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>23.40486279589778</v>
+        <v>23.32996487149808</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>21.15326061928431</v>
+        <v>21.0854475825754</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>57</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.879403232491477</v>
+        <v>-6.857844744155543</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.228599241704202</v>
+        <v>-3.21845545887755</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.379638326413193</v>
+        <v>-5.362967749199129</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.250490771539454</v>
+        <v>-5.234586216558682</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-5.790701723442439</v>
+        <v>-5.772956662498132</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-5.494549550535595</v>
+        <v>-5.477000113280582</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-5.580806345740093</v>
+        <v>-5.562881812507761</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.7779950923653232</v>
+        <v>-0.7753280419448956</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.676377292195134</v>
+        <v>2.667985407321638</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.583373880771667</v>
+        <v>3.571962703884033</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.897360638616746</v>
+        <v>-1.890960407382707</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1039037341491493</v>
+        <v>-0.1036254483652357</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.993979468151998</v>
+        <v>2.98408818974751</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.485250290176609</v>
+        <v>1.480184424679862</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.506561679790629</v>
+        <v>3.545089545209755</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9.897551332235132</v>
+        <v>10.00129430388237</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.17314738958389</v>
+        <v>12.3018790196649</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.634962000676211</v>
+        <v>5.696879009577295</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2413281405973962</v>
+        <v>-0.2407826157944299</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.396395358265664</v>
+        <v>5.453074865406904</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.642106480766692</v>
+        <v>2.669855083085046</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.510364930164059</v>
+        <v>3.546340569918875</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.113993709122362</v>
+        <v>2.135161896321044</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.598910715393309</v>
+        <v>2.62541161093727</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>5.067723050023794</v>
+        <v>5.11949612882426</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.440887439284687</v>
+        <v>6.507998661110868</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.021159109554155</v>
+        <v>6.084452743340663</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>9.699998213811639</v>
+        <v>9.801663798792845</v>
       </c>
     </row>
     <row r="10">
@@ -780,49 +780,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.931640567401239</v>
+        <v>-1.945643540398436</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4.323163443508243</v>
+        <v>4.3620052845949</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.053575394945526</v>
+        <v>5.100064076176039</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.060885320987772</v>
+        <v>4.098862810833538</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10.27159563186025</v>
+        <v>10.36078289001406</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.821594531978171</v>
+        <v>3.855229563511443</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.7638346502485049</v>
+        <v>-0.7696086805961357</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.521823155540353</v>
+        <v>5.568586842236435</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.713959802167089</v>
+        <v>7.778753013092512</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1063792013391662</v>
+        <v>0.1072818860829088</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.351969533282542</v>
+        <v>-2.3717312490189</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.190870601069875</v>
+        <v>-1.199723192683535</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.9758003297861038</v>
+        <v>-0.9824555678832212</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.982585811394436</v>
+        <v>-3.005461508334207</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1857460125176615</v>
+        <v>-0.1851140252205141</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.127257155599146</v>
+        <v>5.199695610157981</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.424832727168763</v>
+        <v>2.464350289502008</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7.175133406173138</v>
+        <v>7.276546779812286</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.17836324355887</v>
+        <v>8.292934163485022</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>10.01875395082907</v>
+        <v>10.15375453461024</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8.395389677249824</v>
+        <v>8.506529658109997</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>7.929781329273666</v>
+        <v>8.035911317420165</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.245386357563774</v>
+        <v>3.289890012792974</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.08040153904060077</v>
+        <v>0.08149818386529262</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.851580390153295</v>
+        <v>1.875328604846601</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.7754977856704599</v>
+        <v>0.7872308612440122</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.182210246200597</v>
+        <v>-1.195523749700179</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.249603897998412</v>
+        <v>-3.289552417424602</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-6.841264407166335</v>
+        <v>-6.874435670871513</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-12.80411886018232</v>
+        <v>-12.86549746626781</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-12.47755891939623</v>
+        <v>-12.53675474876199</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-13.07567453779134</v>
+        <v>-13.13723434617165</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.363557258937071</v>
+        <v>-6.391242562673305</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-12.59854988286526</v>
+        <v>-12.65870203762532</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-14.13899283974636</v>
+        <v>-14.20817080000764</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-18.24123467642588</v>
+        <v>-18.33065693030334</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-14.67640768583104</v>
+        <v>-14.74879263391689</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-14.39555106985733</v>
+        <v>-14.46780955572545</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-15.32563052118535</v>
+        <v>-15.40248988734213</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-18.19718457840678</v>
+        <v>-18.28781475919378</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-17.88897917263325</v>
+        <v>-17.9781423628399</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-15.46150813036027</v>
+        <v>-15.53864000866547</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>171</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.955426624303549</v>
+        <v>-3.945975994520367</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-10.24837556031615</v>
+        <v>-10.22427356072452</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-11.23156205892225</v>
+        <v>-11.20542117763897</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-12.8603166116562</v>
+        <v>-12.83056476965579</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-8.718821581759592</v>
+        <v>-8.699615043997809</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-7.838394411648473</v>
+        <v>-7.820133038652081</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-9.683667868840111</v>
+        <v>-9.660245024666821</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-8.396897684320315</v>
+        <v>-8.37632681033076</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-10.80546727890108</v>
+        <v>-10.77907934231133</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-9.899659443105428</v>
+        <v>-9.874818562427116</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-11.27732873261131</v>
+        <v>-11.24916253001968</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.967117683224103</v>
+        <v>-5.951621477937408</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-9.905512967329514</v>
+        <v>-9.880648018706744</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-10.24123758030655</v>
+        <v>-10.21572200806788</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.156989722079139</v>
+        <v>-0.157928878791985</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.171568650727984</v>
+        <v>-3.180396535770974</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.438118411468388</v>
+        <v>-5.452330947142123</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.503133299269898</v>
+        <v>-2.510034754452043</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-6.785530849192497</v>
+        <v>-6.801698661620556</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.342083951303231</v>
+        <v>-1.345977015054828</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.832857060065699</v>
+        <v>-2.841501698459865</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.84937235595951</v>
+        <v>1.852203351829772</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.987207895998068</v>
+        <v>2.992438654558541</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2019299765768281</v>
+        <v>-0.2051043708449782</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.4059514619732241</v>
+        <v>-0.409857695162458</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.650679558168385</v>
+        <v>-3.661859514342837</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-4.537726768911753</v>
+        <v>-4.551597693362865</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-5.693725660154129</v>
+        <v>-5.71032706531193</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>293</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.2750082860802792</v>
+        <v>-0.2737233481349506</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.161027347855601</v>
+        <v>0.1622336093150167</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.2343368826283765</v>
+        <v>-0.2319994182926592</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.812312952015709</v>
+        <v>-1.806684001626181</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.065829713957342</v>
+        <v>1.063760880653774</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.003707742090540478</v>
+        <v>-0.002854456099129266</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.115979723446976</v>
+        <v>-1.111013259502577</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.926441995598672</v>
+        <v>-1.920203081460976</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.014234790610516</v>
+        <v>-3.005093752626216</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.7883486753695195</v>
+        <v>-0.783546582705263</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.401058342913537</v>
+        <v>1.400778591270601</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.6170524608453576</v>
+        <v>-0.6126198213498526</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.72329148641677</v>
+        <v>-1.71546828895012</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.4466212658029178</v>
+        <v>-0.4418561716908158</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.29399233683047</v>
+        <v>-4.310356138625949</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.305662408103075</v>
+        <v>-2.31637533712027</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4843028195540029</v>
+        <v>-0.4889396888090829</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.741006703653518</v>
+        <v>-1.749776762465565</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-3.667596263044402</v>
+        <v>-3.681126349130828</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.772403217472828</v>
+        <v>-3.78718423438162</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.303038777944884</v>
+        <v>-3.318784507468543</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.27986287609864</v>
+        <v>-5.30179966659032</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-5.062304651357152</v>
+        <v>-5.084248020739203</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-5.075761052398441</v>
+        <v>-5.098718609666854</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-5.002577797801791</v>
+        <v>-5.024920401951</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-6.078200666486595</v>
+        <v>-6.104743372739343</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.164708007283465</v>
+        <v>-3.182379599283003</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.581611697277452</v>
+        <v>-4.60396745920734</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.364239353801771</v>
+        <v>-2.376791602490961</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-4.495276663879622</v>
+        <v>-4.516501515373172</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-6.297895836802653</v>
+        <v>-6.32541214514174</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-9.016270924610176</v>
+        <v>-9.054299864821445</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-7.230423466099438</v>
+        <v>-7.260233611494563</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-7.191747025827361</v>
+        <v>-7.2225319335191</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-6.094324337988738</v>
+        <v>-6.123911930363597</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-6.300936544935865</v>
+        <v>-6.331355069404715</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-4.031993632397992</v>
+        <v>-4.054692617924751</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.325162071320008</v>
+        <v>-3.34637624451117</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.49455245679804</v>
+        <v>-2.512168529867587</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.389142472708528</v>
+        <v>-0.399863294600145</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.2900603943755371</v>
+        <v>-0.3006373860644658</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.076002950003783</v>
+        <v>-1.089877092749212</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7874015748032335</v>
+        <v>0.7862361322873213</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.726333071916279</v>
+        <v>-1.732075311407314</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7674293263981085</v>
+        <v>0.7651050299118793</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.210793776299298</v>
+        <v>2.209735832836124</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.09495389784128605</v>
+        <v>0.09195127776451528</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.443548772329422</v>
+        <v>1.442024794427482</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.673854745563112</v>
+        <v>2.673080550839522</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.419126174652909</v>
+        <v>1.416423467847387</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.248465565051141</v>
+        <v>4.250160423770431</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.399944567288415</v>
+        <v>3.400035238742539</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.406739356300854</v>
+        <v>2.405808230214312</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.229295411226616</v>
+        <v>3.229665071770356</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.335279867755794</v>
+        <v>3.335726250299054</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.585001200032082</v>
+        <v>3.585447582575341</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7960353640005096</v>
+        <v>0.7935507683857423</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.473935435246815</v>
+        <v>2.472492257341052</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.1053825181239105</v>
+        <v>0.09866315286776484</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.879526316540193</v>
+        <v>1.876390158187</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.188681950614701</v>
+        <v>2.187660848721606</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.47320854610539</v>
+        <v>3.475201796338261</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.415204478533241</v>
+        <v>1.410270059264001</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.596008899335636</v>
+        <v>2.593251676984146</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.1003631192890708</v>
+        <v>-0.1080122356008317</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.673916243942422</v>
+        <v>2.672225615674904</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.798490793966565</v>
+        <v>2.797505294657661</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.186234579603408</v>
+        <v>1.181723435501475</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.413068822992116</v>
+        <v>2.411633841058148</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.662790155268404</v>
+        <v>2.661355173334435</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.7953251126627592</v>
+        <v>-0.8057485281052905</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.9893276894672312</v>
+        <v>0.9811510279011131</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.9149749793934632</v>
+        <v>-0.9307272983680335</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.5669336015294633</v>
+        <v>-0.5817487192845405</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.860601052278653</v>
+        <v>-1.877745691932461</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.810029897065867</v>
+        <v>-0.8227279966410492</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.8900003234333695</v>
+        <v>-0.9074617139133281</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.9774435861964221</v>
+        <v>-0.9958572339069462</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.41712509930715</v>
+        <v>-1.43564499887713</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.7546407948010838</v>
+        <v>-0.7706186687534995</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.959394119118663</v>
+        <v>-0.9753719930710787</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.05708643347139</v>
+        <v>-2.077352472089323</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.6086226342969</v>
+        <v>-3.633970719397816</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-2.981542811454574</v>
+        <v>-3.005461508333653</v>
       </c>
     </row>
     <row r="21">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.2415</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4080~4093</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4080</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.1846183837330599</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.2202</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4054~4067</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4054</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.1944464342989818</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.199</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4014~4027</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4014</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.2957725640639595</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.1778</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3957~3970</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3957</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.2012468844417086</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.1566</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3883~3895</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3883</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.2726424280405269</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.1354</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3795~3806</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3795</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.2338481993481736</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.1142</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3667~3676</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3667</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.2355493104167152</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.09303</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3530~3538</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3530</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.02210718572558079</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.07183</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3359~3367</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3359</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.2241143973427455</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.05063</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3146~3153</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3146</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.2499806458540945</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.02942</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2853~2860</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2853</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.3037644769928249</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.008221</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2494~2499</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2494</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.9679462336115563</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 0.01298</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2109~2112</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2109</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.578531376759727</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.03418</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1729~1731</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1729</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.752662199720696</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.05539</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1426~1427</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1426</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.956456564162835</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.07659</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1162~1162</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1162</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>2.584014347604132</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.09779</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>956~956</t>
-        </is>
+      <c r="B22" t="n">
+        <v>956</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>3.573507286484585</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.119</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>798~798</t>
-        </is>
+      <c r="B23" t="n">
+        <v>798</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>4.022852406607065</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.1402</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>675~675</t>
-        </is>
+      <c r="B24" t="n">
+        <v>675</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>4.247302420530758</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.1614</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>588~588</t>
-        </is>
+      <c r="B25" t="n">
+        <v>588</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>4.309282768225394</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.1826</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>496~496</t>
-        </is>
+      <c r="B26" t="n">
+        <v>496</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>5.772690712048089</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.2038</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>419~419</t>
-        </is>
+      <c r="B27" t="n">
+        <v>419</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>5.74045189458716</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.225</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>350~350</t>
-        </is>
+      <c r="B28" t="n">
+        <v>350</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>5.22084739407574</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.2462</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>300~300</t>
-        </is>
+      <c r="B29" t="n">
+        <v>300</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>3.506561679790032</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.2674</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>243~243</t>
-        </is>
+      <c r="B30" t="n">
+        <v>243</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>2.239071967855864</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.2886</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>196~196</t>
-        </is>
+      <c r="B31" t="n">
+        <v>196</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>2.098398414483903</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.3098</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>151~151</t>
-        </is>
+      <c r="B32" t="n">
+        <v>151</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.1755575255079904</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.331</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>123~123</t>
-        </is>
+      <c r="B33" t="n">
+        <v>123</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>1.978106395237177</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.3522</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>103~103</t>
-        </is>
+      <c r="B34" t="n">
+        <v>103</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>2.846367505032738</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.3734</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>2.268466441694791</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.2415</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>9.41132358455193</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.2202</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>110~110</t>
-        </is>
+      <c r="B7" t="n">
+        <v>110</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>7.506561679790025</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.199</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>150~150</t>
-        </is>
+      <c r="B8" t="n">
+        <v>150</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>8.173228346456696</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.1778</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>207~207</t>
-        </is>
+      <c r="B9" t="n">
+        <v>207</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>4.028300810224806</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.1566</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>281~282</t>
-        </is>
+      <c r="B10" t="n">
+        <v>281</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>3.889540403194275</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.1354</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>369~371</t>
-        </is>
+      <c r="B11" t="n">
+        <v>369</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>2.493084590841242</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.1142</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>497~501</t>
-        </is>
+      <c r="B12" t="n">
+        <v>497</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>1.797978845458687</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.09303</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>634~639</t>
-        </is>
+      <c r="B13" t="n">
+        <v>634</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.0677732184885329</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.07183</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>805~810</t>
-        </is>
+      <c r="B14" t="n">
+        <v>805</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.8885000486050387</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.05063</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1018~1024</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1018</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.7356258202099752</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.02942</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1311~1317</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1311</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.6331497856617574</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.008221</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1670~1678</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1670</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-1.420732718302943</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 0.01298</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2055~2065</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2055</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-1.597554542970258</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.03418</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2435~2446</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2435</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-1.226063013586923</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.05539</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2738~2750</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2738</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-1.00252922930089</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.07659</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3002~3015</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3002</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.9843172588501119</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.09779</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3208~3221</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3208</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-1.049787280160302</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.119</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3366~3379</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3366</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.9397242036074331</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.1402</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3489~3502</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3489</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.8086867496788486</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.1614</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3576~3589</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3576</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.6962803374849784</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.1826</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3668~3681</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3668</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.7683636122501838</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.2038</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3745~3758</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3745</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.6307453984430822</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.225</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3814~3827</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3814</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.4683533972938534</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.2462</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3864~3877</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3864</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.2623317945458012</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.2674</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3921~3934</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3921</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.1294322195490665</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.2886</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3968~3981</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3968</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.09454357014718084</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.3098</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4013~4026</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4013</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.01525517209007887</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.331</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4041~4054</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4041</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.0514057597758395</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.3522</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4061~4074</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4061</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.06339413758846746</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.3734</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4080~4093</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4080</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.03802664173452541</v>

--- a/workspaces/btc_daily_14days/roc/roc_14.xlsx
+++ b/workspaces/btc_daily_14days/roc/roc_14.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ROC-14 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ROC-14 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.347801500660303</v>
+        <v>1.36028416735796</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-7.927769947260316</v>
+        <v>-7.914904876503464</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.019230691089255</v>
+        <v>7.032206623970168</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>18.66073935947623</v>
+        <v>18.6736973891183</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.777702018568441</v>
+        <v>2.790784801128268</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.7631151018951243</v>
+        <v>-0.7500987906748477</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.67083282704066</v>
+        <v>10.68388056887207</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.99525378145696</v>
+        <v>-8.982096046307795</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.375458579465771</v>
+        <v>-1.362277008272919</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.459641929526136</v>
+        <v>5.473034750972317</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.256353500599104</v>
+        <v>5.269801475051182</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9.136187125915882</v>
+        <v>9.149633686598143</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.873043364009362</v>
+        <v>4.886596255948248</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.970062967190785</v>
+        <v>8.959633331492633</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>40</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.973630687616719</v>
+        <v>9.986119660628987</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>15.84769097260568</v>
+        <v>15.86057286485647</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>12.96415945404453</v>
+        <v>12.9771390010881</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.615550010409443</v>
+        <v>5.628499809698482</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>17.55215992666621</v>
+        <v>17.56525050866519</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.378512635234102</v>
+        <v>5.391531547451734</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.79964075304585</v>
+        <v>2.812684853622009</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9.822991870326227</v>
+        <v>9.836156164068363</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7.267652794351854</v>
+        <v>7.280836754026808</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.917649426428099</v>
+        <v>8.931042924355125</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>16.20964471435941</v>
+        <v>16.22309458830271</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>16.24795576242778</v>
+        <v>16.26140312916834</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>23.32996487149808</v>
+        <v>23.34351886124001</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>21.0854475825754</v>
+        <v>21.07501794687838</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>57</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.857844744155543</v>
+        <v>-6.845370306823241</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.21845545887755</v>
+        <v>-3.205588520926327</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.362967749199129</v>
+        <v>-5.350001490508532</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.234586216558682</v>
+        <v>-5.221643953315123</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-5.772956662498132</v>
+        <v>-5.759879702370874</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-5.477000113280582</v>
+        <v>-5.463987254187202</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-5.562881812507761</v>
+        <v>-5.549841953883245</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.7753280419448956</v>
+        <v>-0.7621681217088394</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.667985407321638</v>
+        <v>2.681167593247046</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.571962703884033</v>
+        <v>3.585354607019575</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.890960407382707</v>
+        <v>-1.877514105689031</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1036254483652357</v>
+        <v>-0.09018023954200061</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.98408818974751</v>
+        <v>2.997640866024732</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.480184424679862</v>
+        <v>1.46975478898171</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.545089545209755</v>
+        <v>3.506667978168721</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>10.00129430388237</v>
+        <v>9.877104668032437</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.3018790196649</v>
+        <v>12.14477601272382</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.696879009577295</v>
+        <v>5.628022218498764</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2407826157944299</v>
+        <v>-0.2284243643255834</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.453074865406904</v>
+        <v>5.391207281987342</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.669855083085046</v>
+        <v>2.646236251940984</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.546340569918875</v>
+        <v>3.511970374933064</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.135161896321044</v>
+        <v>2.120375911380286</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.62541161093727</v>
+        <v>2.603789799208265</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>5.11949612882426</v>
+        <v>5.064540729333267</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.507998661110868</v>
+        <v>6.432777013307593</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.084452743340663</v>
+        <v>6.014381836068218</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>9.801663798792845</v>
+        <v>10.24168461354451</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>88</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.945643540398436</v>
+        <v>-1.9325722118149</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4.3620052845949</v>
+        <v>4.373812448150822</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.100064076176039</v>
+        <v>5.111732318731818</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.098862810833538</v>
+        <v>4.110773445472738</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10.36078289001406</v>
+        <v>10.37122139840336</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.855229563511443</v>
+        <v>3.867348463631657</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.7696086805961357</v>
+        <v>-0.7562238034534445</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.568586842236435</v>
+        <v>5.580439829215138</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.778753013092512</v>
+        <v>7.790060450006713</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1072818860829088</v>
+        <v>0.1208110230070858</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.3717312490189</v>
+        <v>-2.357495314682161</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.199723192683535</v>
+        <v>-1.185832027903828</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.9824555678832212</v>
+        <v>-1.610517815698863</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.005461508334207</v>
+        <v>-3.015891144032359</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>128</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1851140252205141</v>
+        <v>-0.1724284172896162</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.199695610157981</v>
+        <v>5.21127129490511</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.464350289502008</v>
+        <v>2.476718301563771</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7.276546779812286</v>
+        <v>7.287591094909175</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.292934163485022</v>
+        <v>8.303839266586778</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>10.15375453461024</v>
+        <v>10.16416600446627</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8.506529658109997</v>
+        <v>8.51746999087726</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>8.035911317420165</v>
+        <v>8.04707655695114</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.289890012792974</v>
+        <v>3.302371923278798</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.08149818386529262</v>
+        <v>0.0951068437275211</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.875328604846601</v>
+        <v>1.448998571482804</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.7872308612440122</v>
+        <v>0.362310520880861</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.195523749700179</v>
+        <v>-1.181967703348576</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.289552417424602</v>
+        <v>-3.299982053122754</v>
       </c>
     </row>
     <row r="12">
@@ -887,514 +887,514 @@
         <v>137</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-6.874435670871513</v>
+        <v>-6.859970128177352</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-12.86549746626781</v>
+        <v>-12.84904243899294</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-12.53675474876199</v>
+        <v>-12.52032035724885</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-13.13723434617165</v>
+        <v>-13.12068940056547</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.391242562673305</v>
+        <v>-6.376477851679446</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-12.65870203762532</v>
+        <v>-12.64216200691355</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-14.20817080000764</v>
+        <v>-14.19109033441062</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-18.33065693030334</v>
+        <v>-18.31230849226274</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-14.74879263391689</v>
+        <v>-14.73138599256595</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-14.46780955572545</v>
+        <v>-14.86354562954703</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-15.40248988734213</v>
+        <v>-15.38903259363191</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-18.28781475919378</v>
+        <v>-18.27436247047367</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-17.9781423628399</v>
+        <v>-17.9645863164883</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-15.53864000866547</v>
+        <v>-15.54906964436363</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.08243</t>
+          <t>X ≈ -0.08244</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>171</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.945975994520367</v>
+        <v>-3.932315186033691</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-10.22427356072452</v>
+        <v>-10.20839442447305</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-11.20542117763897</v>
+        <v>-11.1891851403291</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-12.83056476965579</v>
+        <v>-12.81390052386956</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-8.699615043997809</v>
+        <v>-8.684129810327242</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-7.820133038652081</v>
+        <v>-7.804828514320825</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-9.660245024666821</v>
+        <v>-9.644267385843207</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-8.37632681033076</v>
+        <v>-8.360585309472789</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-10.77907934231133</v>
+        <v>-10.76258777296103</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-9.874818562427116</v>
+        <v>-9.861413434774285</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-11.24916253001968</v>
+        <v>-11.23570523630946</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.951621477937408</v>
+        <v>-5.938169189217298</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-9.880648018706744</v>
+        <v>-9.867091972355141</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-10.21572200806788</v>
+        <v>-10.22615164376603</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.06123</t>
+          <t>X ≈ -0.06124</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>213</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.157928878791985</v>
+        <v>-0.1452518618396255</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.180396535770974</v>
+        <v>-3.166307869518256</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.452330947142123</v>
+        <v>-5.437444238214702</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.510034754452043</v>
+        <v>-2.496114263017112</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-6.801698661620556</v>
+        <v>-6.786444352868159</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.345977015054828</v>
+        <v>-1.33237024611617</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.841501698459865</v>
+        <v>-2.827251549216413</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.852203351829772</v>
+        <v>1.865091141558274</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.992438654558541</v>
+        <v>2.742391249985452</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2051043708449782</v>
+        <v>-0.1916992431921472</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.409857695162458</v>
+        <v>-0.3964004014522402</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.661859514342837</v>
+        <v>-3.648407225622726</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-4.551597693362865</v>
+        <v>-4.538041647011262</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-5.71032706531193</v>
+        <v>-5.720756701010082</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.04003</t>
+          <t>X ≈ -0.04004</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>293</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.2737233481349506</v>
+        <v>-0.2610647696319575</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1622336093150167</v>
+        <v>0.1752728129752938</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.2319994182926592</v>
+        <v>-0.2186958306351201</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.806684001626181</v>
+        <v>-1.792932587654782</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.063760880653774</v>
+        <v>1.076552048370829</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.002854456099129266</v>
+        <v>0.01029187849085389</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.111013259502577</v>
+        <v>-1.097250381952016</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.920203081460976</v>
+        <v>-1.906137322094779</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-3.005093752626216</v>
+        <v>-2.991895013671453</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.783546582705263</v>
+        <v>-0.7701414550524319</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.400778591270601</v>
+        <v>1.414235884980819</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.6126198213498526</v>
+        <v>-0.5991675326297425</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.71546828895012</v>
+        <v>-1.701912242598517</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.4418561716908158</v>
+        <v>-0.452285807388968</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.01882</t>
+          <t>X ≈ -0.01884</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>359</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.310356138625949</v>
+        <v>-4.29592992890246</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.31637533712027</v>
+        <v>-2.302188542410896</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4889396888090829</v>
+        <v>-0.4753325157155217</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.749776762465565</v>
+        <v>-1.735723167941892</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-3.681126349130828</v>
+        <v>-3.666395255012112</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.78718423438162</v>
+        <v>-3.927159386893386</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.318784507468543</v>
+        <v>-3.30389215707374</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.30179966659032</v>
+        <v>-5.444681691535273</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-5.084248020739203</v>
+        <v>-5.07104928178444</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-5.098718609666854</v>
+        <v>-5.085313482014023</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-5.024920401951</v>
+        <v>-5.011463108240783</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-6.104743372739343</v>
+        <v>-6.091291084019232</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.182379599283003</v>
+        <v>-3.1688235529314</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.60396745920734</v>
+        <v>-4.614397094905492</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 0.00238</t>
+          <t>X ≈ 0.002368</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.376791602490961</v>
+        <v>-2.492289808522344</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-4.516501515373172</v>
+        <v>-4.631941521259868</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-6.32541214514174</v>
+        <v>-6.591577907920801</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-9.054299864821445</v>
+        <v>-9.178773891090785</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-7.260233611494563</v>
+        <v>-7.379581771364215</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-7.2225319335191</v>
+        <v>-7.346499258966986</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-6.123911930363597</v>
+        <v>-6.391734835334013</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-6.331355069404715</v>
+        <v>-6.451426224611701</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-4.054692617924751</v>
+        <v>-4.168658381134485</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.34637624451117</v>
+        <v>-3.456077177464344</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.512168529867587</v>
+        <v>-2.619111669057865</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.399863294600145</v>
+        <v>-0.5014001833691495</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.3006373860644658</v>
+        <v>-0.4007177033492866</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.089877092749212</v>
+        <v>-1.216648719789418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.02358</t>
+          <t>X ≈ 0.02357</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7862361322873213</v>
+        <v>0.7795032130017674</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.732075311407314</v>
+        <v>-1.741821039413523</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7651050299118793</v>
+        <v>0.8954196362507147</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.209735832836124</v>
+        <v>2.336956821501893</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.09195127776451528</v>
+        <v>0.2242801047941398</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.442024794427482</v>
+        <v>1.570415114399204</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.673080550839522</v>
+        <v>2.798040713138285</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.416423467847387</v>
+        <v>1.543570494548398</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.250160423770431</v>
+        <v>4.369727445637203</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.400035238742539</v>
+        <v>3.519808649307308</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.405808230214312</v>
+        <v>2.527705916243967</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.229665071770356</v>
+        <v>3.349485643402417</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.335726250299054</v>
+        <v>3.454269173291131</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.585447582575341</v>
+        <v>3.680004823517663</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.04479</t>
+          <t>X ≈ 0.04477</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.7935507683857423</v>
+        <v>0.9823937829292788</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.472492257341052</v>
+        <v>2.672612037342518</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.09866315286776484</v>
+        <v>0.2923262682438903</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.876390158187</v>
+        <v>1.745524389975273</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.187660848721606</v>
+        <v>2.199576494726031</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.475201796338261</v>
+        <v>3.680581807138772</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.410270059264001</v>
+        <v>1.609116480985151</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.593251676984146</v>
+        <v>2.79767697627134</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.1080122356008317</v>
+        <v>0.08768819723192678</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.672225615674904</v>
+        <v>2.880153506862371</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>2.797505294657661</v>
+        <v>3.006578176416753</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.181723435501475</v>
+        <v>1.385327189699261</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.411633841058148</v>
+        <v>2.620805475458667</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.661355173334435</v>
+        <v>2.846541125685199</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.06599</t>
+          <t>X ≈ 0.06597</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.8057485281052905</v>
+        <v>-0.9881302369716281</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.9811510279011131</v>
+        <v>0.7863398192166429</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.9307272983680335</v>
+        <v>-1.119715324324922</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.5817487192845405</v>
+        <v>-0.6121316901705214</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.877745691932461</v>
+        <v>-2.064749238615271</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.8227279966410492</v>
+        <v>-1.012658227848107</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.9074617139133281</v>
+        <v>-1.097368587114232</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.9958572339069462</v>
+        <v>-1.187078740335025</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.43564499887713</v>
+        <v>-1.62541938742379</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.7706186687534995</v>
+        <v>-0.9659042214894527</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.9753719930710787</v>
+        <v>-1.170605379749645</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.077352472089323</v>
+        <v>-2.26830269909248</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.633970719397816</v>
+        <v>-3.820529024104005</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.005461508333653</v>
+        <v>-3.217434883311434</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.08719</t>
+          <t>X ≈ 0.08717</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>206</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.00800142700615</v>
+        <v>-1.995479137330527</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-4.590448826378058</v>
+        <v>-4.577539016802007</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-6.311375079978852</v>
+        <v>-6.298395937580388</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.125169891315949</v>
+        <v>-4.112126995021583</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.75359292897658</v>
+        <v>-2.740526674676104</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.3081549685347795</v>
+        <v>-0.2949739592395417</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.310902427532611</v>
+        <v>-2.297703688577847</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.617338292172242</v>
+        <v>-4.603933164519411</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.909470257266527</v>
+        <v>-1.896012963556309</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.875087099921096</v>
+        <v>-1.861634811200986</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.809904817662058</v>
+        <v>-1.796348771310456</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.074746592181889</v>
+        <v>-1.085176227880041</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.304030034220403</v>
+        <v>1.022268682841407</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.489924775686525</v>
+        <v>3.232738640733025</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.829233284279809</v>
+        <v>1.564081905659521</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.0607522396721194</v>
+        <v>0.4204216989293741</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.110580367805149</v>
+        <v>-1.391753204484758</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-7.142252354140084</v>
+        <v>-7.463805926442028</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-4.062429109387047</v>
+        <v>-4.363802909912017</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.89670111576352</v>
+        <v>-3.556986203380283</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.590612394350849</v>
+        <v>-4.254911035062264</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.643269224948398</v>
+        <v>-1.920116455595981</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.05071162794921236</v>
+        <v>-0.2139895883784604</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.983828962509911</v>
+        <v>1.731216589454647</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.563574351564931</v>
+        <v>1.31106573614116</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.446207076246289</v>
+        <v>2.173744061526925</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>123</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.791114525318527</v>
+        <v>3.6166449450755</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>11.74864660341114</v>
+        <v>11.76155641298719</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>15.41881854722105</v>
+        <v>15.43182567863865</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>14.73606354974725</v>
+        <v>13.93603456206446</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>10.13260168426862</v>
+        <v>10.1457124886435</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>7.991019231740324</v>
+        <v>8.004062128034647</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>7.906285514468046</v>
+        <v>7.919351768768522</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>6.626093985605301</v>
+        <v>5.826266864819189</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>5.75208596934165</v>
+        <v>4.952276578215063</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>9.780009564801489</v>
+        <v>9.793414692454363</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>7.136231850240044</v>
+        <v>7.149689143950262</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>5.544598747422874</v>
+        <v>5.558051036143034</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.685319746234114</v>
+        <v>2.698875792585675</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>7.000081728916861</v>
+        <v>6.989652093218751</v>
       </c>
     </row>
     <row r="24">
@@ -1508,49 +1508,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.828400760249728</v>
+        <v>3.200902151283771</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.366252434641858</v>
+        <v>3.862443330947279</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.6725331533326226</v>
+        <v>1.19494467346496</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.40048743536542</v>
+        <v>5.870624362507868</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>6.011491507649566</v>
+        <v>6.468698445775814</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>8.607784020077872</v>
+        <v>9.038799748138238</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.523050302805594</v>
+        <v>8.954089388871999</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.458165754598795</v>
+        <v>3.941566199630721</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.05110999365246727</v>
+        <v>0.471493134017031</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>3.696465970744953</v>
+        <v>4.167028883141718</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.255413790354289</v>
+        <v>-1.719490456936661</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-3.370455920365181</v>
+        <v>-2.821475940945035</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.491859956597509</v>
+        <v>-0.9688995215311067</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.09271333696483453</v>
+        <v>0.393199765059002</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>92</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3.580394841949108</v>
+        <v>-3.567872552273485</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.329770675521424</v>
+        <v>1.342680485097475</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.021858490663959</v>
+        <v>2.034865622081561</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.02180142020673514</v>
+        <v>-0.00882227780827094</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.787603451677555</v>
+        <v>3.800714256052494</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.8241758241757537</v>
+        <v>0.8372187204701191</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.913355150381804</v>
+        <v>2.92642140468228</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.533128273339493</v>
+        <v>3.546309282634731</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.55908490889626</v>
+        <v>4.572283647851023</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.812779406566442</v>
+        <v>-2.799374278913611</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-9.504888703973378</v>
+        <v>-9.491436415253268</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-7.751230271440022</v>
+        <v>-7.737674225088419</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-5.327595895685469</v>
+        <v>-5.338025531383622</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>77</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>5.948120121348467</v>
+        <v>5.960642411024089</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>10.8300530018907</v>
+        <v>10.84296281146675</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.53908039919029</v>
+        <v>6.552087530607892</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7.968034830498873</v>
+        <v>7.981013972897337</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>10.02701621282944</v>
+        <v>10.04012701720438</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>11.62315944924649</v>
+        <v>11.63620234554085</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>12.83712703067543</v>
+        <v>12.8501932849759</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>12.36994363189378</v>
+        <v>12.38312464118902</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>12.30894374571154</v>
+        <v>12.3221424846663</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>12.75751985938491</v>
+        <v>12.77092498703774</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>11.25406523636619</v>
+        <v>11.26752253007641</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>11.28844839371146</v>
+        <v>11.30190068243157</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>14.76429767887054</v>
+        <v>14.77785372522214</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.221811218939031</v>
+        <v>7.211381583240879</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>69</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>8.376126897181337</v>
+        <v>8.388649186856959</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>9.663104008854745</v>
+        <v>9.676013818430796</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.369684577620397</v>
+        <v>6.382691709037999</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.050662347909231</v>
+        <v>5.063641490307695</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.96151649515582</v>
+        <v>5.974627299530759</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>6.258958432871431</v>
+        <v>6.272001329165796</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>7.623500077918031</v>
+        <v>7.636566332218507</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.605592041455417</v>
+        <v>8.618773050750654</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.5445921552732</v>
+        <v>8.557790894227963</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>10.59301769488295</v>
+        <v>10.60642282253578</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.938989008246324</v>
+        <v>8.952446301956542</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>19.1182997018238</v>
+        <v>19.13175199054391</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>14.35021900392226</v>
+        <v>14.36377505027386</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>13.15066497387974</v>
+        <v>13.14023533818159</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>15.50656167978997</v>
+        <v>16.90683907150646</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>9.894988066825768</v>
+        <v>11.21402032538141</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>17.50011936022918</v>
+        <v>18.98251424674883</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>11.63037249283668</v>
+        <v>12.99029041074534</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>13.09195127776451</v>
+        <v>14.49281718418026</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>21.38939321548023</v>
+        <v>20.91264019340724</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>17.30465949820789</v>
+        <v>16.7462971810798</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>14.83747609942645</v>
+        <v>14.2384122107625</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>14.77647621324409</v>
+        <v>14.17743005423966</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.926351028216104</v>
+        <v>7.205062278317911</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>13.72159770389858</v>
+        <v>13.12281009964961</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>17.75598086124401</v>
+        <v>17.23882090506617</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>17.33572625029922</v>
+        <v>16.81867005175276</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>19.5854475825754</v>
+        <v>19.0852220285099</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>8.910070451719953</v>
+        <v>7.863911555672601</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>10.80726876858019</v>
+        <v>9.701001324677733</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>8.65801409707128</v>
+        <v>7.582092008888161</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>11.16059301454549</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.741074084782007</v>
+        <v>3.725751737311811</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.038516022497667</v>
+        <v>5.747263697981381</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>17.2344840596114</v>
+        <v>17.73151885595664</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>11.50414276609305</v>
+        <v>12.09203641906645</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.688756914998415</v>
+        <v>10.30691633150914</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.838631729970587</v>
+        <v>9.456997535179383</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.3882643705653</v>
+        <v>10.97643430795367</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.668261562998396</v>
+        <v>9.286674529274471</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.59066160699564</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>13.76088617906662</v>
+        <v>14.26467311929104</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>47</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.825710615960176</v>
+        <v>2.838232905635799</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>20.36307317320868</v>
+        <v>20.37598298278473</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>24.22352361554833</v>
+        <v>24.23653074696593</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>22.22611717368775</v>
+        <v>22.23909631608621</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>23.81535553308372</v>
+        <v>23.82846633745866</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>19.85747832186321</v>
+        <v>19.87052121815758</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>21.90040417905896</v>
+        <v>21.91347043335944</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>25.6885399292136</v>
+        <v>25.70172093850883</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>23.49988046856324</v>
+        <v>23.513079207518</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>18.39443613459905</v>
+        <v>18.40784126225188</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>20.31734238474959</v>
+        <v>20.33079967845981</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>22.47938511656317</v>
+        <v>22.49283740528328</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>22.05913050561819</v>
+        <v>22.0726865519698</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>24.43651141236261</v>
+        <v>24.42608177666445</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>45</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>9.728783902012246</v>
+        <v>9.741306191687869</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-5.216123044285375</v>
+        <v>-5.203213234709324</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.277897138006949</v>
+        <v>3.290904269424551</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.408150270614449</v>
+        <v>3.421129413012913</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2.86972905554228</v>
+        <v>2.882839859917219</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.16717099325794</v>
+        <v>3.180213889552306</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.30465949820789</v>
+        <v>5.317725752508366</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.281920543870861</v>
+        <v>9.295101553166099</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>11.44314287991075</v>
+        <v>11.45634161886551</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>17.25968436154952</v>
+        <v>17.27308948920235</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.61048659278751</v>
+        <v>12.62394388649773</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.6448697501329</v>
+        <v>12.65832203885301</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>18.89128180585467</v>
+        <v>18.90483785220627</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>14.69655869368654</v>
+        <v>14.68612905798839</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>28</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-9.636295463067121</v>
+        <v>-9.623773173391498</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-11.24786907603138</v>
+        <v>-11.23495926645533</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.499880639770872</v>
+        <v>-4.48687350835327</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.7981989357346961</v>
+        <v>-0.7852197933362319</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.806236992050174</v>
+        <v>5.819347796425113</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.103678929765834</v>
+        <v>6.1167218260602</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.447516641064986</v>
+        <v>2.460582895365462</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.980333242283585</v>
+        <v>1.993514251578823</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.919333356101284</v>
+        <v>1.932532095056047</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.069208171073356</v>
+        <v>1.082613298726187</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.706973724672949</v>
+        <v>-2.693516430962731</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-6.244019138755931</v>
+        <v>-6.230566850035821</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.4785833931562493</v>
+        <v>0.4921394395078522</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.843123845995976</v>
+        <v>-2.853553481694128</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>20</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.49343832020994</v>
+        <v>-2.480916030534317</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.105011933174168</v>
+        <v>-4.092102123598117</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.5001193602292489</v>
+        <v>0.513126491646851</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.630372492836642</v>
+        <v>5.643351635235106</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>5.091951277764586</v>
+        <v>5.105062082139526</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>10.38939321548024</v>
+        <v>10.40243611177461</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.30465949820796</v>
+        <v>10.31772575250844</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>14.83747609942632</v>
+        <v>14.85065710872156</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>14.77647621324402</v>
+        <v>14.78967495219878</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>13.92635102821609</v>
+        <v>13.93975615586892</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>13.72159770389858</v>
+        <v>13.7350549976088</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>18.75598086124394</v>
+        <v>18.76943314996405</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>13.33572625029915</v>
+        <v>13.34928229665076</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>8.58544758257537</v>
+        <v>8.575017946877217</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>19</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>5.401298521895242</v>
+        <v>5.413820811570865</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-1.47343298580585</v>
+        <v>-1.460523176229799</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-7.131459587139247</v>
+        <v>-7.118452455721645</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-1.73804855979494</v>
+        <v>-1.725069417396476</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>2.986688119869775</v>
+        <v>2.999798924244715</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>13.81044584705911</v>
+        <v>13.82348874335348</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>13.72571212978684</v>
+        <v>13.73877838408731</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>7.995370836268492</v>
+        <v>8.00855184556373</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>23.72384463429672</v>
+        <v>23.73704337325148</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>22.87371944926879</v>
+        <v>22.88712457692162</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>17.40580823021448</v>
+        <v>17.41926552392469</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>17.44019138755979</v>
+        <v>17.4536436762799</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>17.01993677661486</v>
+        <v>17.03349282296647</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>12.00650021415427</v>
+        <v>11.99607057845612</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ROC-14 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ROC-14 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,53 +2210,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.2415</t>
+          <t>X &gt; -0.2414</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4080</v>
+        <v>4081</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1846183837330599</v>
+        <v>-0.1848730407932635</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.02387801333063777</v>
+        <v>-0.02418128313886569</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.1122003659991222</v>
+        <v>-0.11248445654482</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2131482895594061</v>
+        <v>-0.2134071034595522</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1758403583323371</v>
+        <v>-0.1761115119925805</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.08516647140827871</v>
+        <v>-0.08545823892245608</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.009752050605428053</v>
+        <v>-0.01006289719808962</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.07487208572106141</v>
+        <v>0.07453770573655305</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1742730308695428</v>
+        <v>0.1739138166139327</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2192011751309479</v>
+        <v>0.2188259233108525</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2486611376482699</v>
+        <v>0.2482773286567976</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1989009984316681</v>
+        <v>0.1985294027194513</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2335454122692227</v>
+        <v>0.233162747410141</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.203094641398927</v>
+        <v>0.203295329871608</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4054</v>
+        <v>4055</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1944464342989818</v>
+        <v>-0.1947803373190098</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.02681295615188617</v>
+        <v>0.02641275223166417</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1579372203366347</v>
+        <v>-0.1582950528687093</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.3341944362971745</v>
+        <v>-0.3345081433626405</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1947826626735889</v>
+        <v>-0.1951347682542561</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.08081850288517245</v>
+        <v>-0.08119667188285717</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.07825111494158676</v>
+        <v>-0.07863072213466182</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1330426018894428</v>
+        <v>0.1326073672786379</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1842121087848625</v>
+        <v>0.1837636221495842</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1855920336375476</v>
+        <v>0.1851367914935338</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2165447090748245</v>
+        <v>0.2160801331435422</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1415824391532823</v>
+        <v>0.1411363789510602</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2037903686714841</v>
+        <v>0.2033256891556405</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1468684015196473</v>
+        <v>0.1471511158044976</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4014</v>
+        <v>4015</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.2957725640639595</v>
+        <v>-0.296208979888867</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.1308440245800924</v>
+        <v>-0.131337286250286</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2887005155472195</v>
+        <v>-0.2891586549006604</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3934843660102487</v>
+        <v>-0.3939154455101956</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.3716331119943703</v>
+        <v>-0.372075094798916</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1352214041120732</v>
+        <v>-0.1357194934951664</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1069296587182436</v>
+        <v>-0.1074358586303745</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.03648107455076399</v>
+        <v>0.03593440292705452</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1136247576581297</v>
+        <v>0.1130580367759677</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.09857601577216002</v>
+        <v>0.09800447634672338</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.05717151520054387</v>
+        <v>0.05660800905727825</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.01891953716236827</v>
+        <v>-0.01946403699132304</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.02666478332480438</v>
+        <v>-0.02721172725366472</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.06178709604941446</v>
+        <v>-0.06134568948639441</v>
       </c>
     </row>
     <row r="9">
@@ -2370,49 +2370,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3957</v>
+        <v>3958</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2012468844417086</v>
+        <v>-0.2018931143923268</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.0863674383392663</v>
+        <v>-0.08706434022285947</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.2156064462224379</v>
+        <v>-0.2162763806132375</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3237490095580711</v>
+        <v>-0.3243903002487301</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2938278447770983</v>
+        <v>-0.2944841744776454</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.05827387153117769</v>
+        <v>-0.05898597597130362</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.02833747454690183</v>
+        <v>-0.02905861066943771</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.04817506485661482</v>
+        <v>0.04742804716764226</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.07682957013454939</v>
+        <v>0.07607414472975904</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.04854239403287153</v>
+        <v>0.04778240523799582</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.085234067534941</v>
+        <v>0.08446171308469275</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.01769936103434588</v>
+        <v>-0.01844563791466669</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.07003423479437032</v>
+        <v>-0.07077327293756497</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.08399896784158045</v>
+        <v>-0.08339539319349853</v>
       </c>
     </row>
     <row r="10">
@@ -2425,46 +2425,46 @@
         <v>3883</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2726424280405269</v>
+        <v>-0.2735238334090937</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.278612344062779</v>
+        <v>-0.2795218925327134</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.4541575470402748</v>
+        <v>-0.455029646000888</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4384867055189261</v>
+        <v>-0.4393609257717941</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2948387505058534</v>
+        <v>-0.2957601172439013</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1633060133116047</v>
+        <v>-0.1642562552262348</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.07975808986102351</v>
+        <v>-0.0807318310391949</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.01849097876290529</v>
+        <v>-0.01948945851930262</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.03760304627727606</v>
+        <v>0.03658853244576221</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.0005661102295348996</v>
+        <v>-0.001586782129457731</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.01070602840515278</v>
+        <v>-0.01172832714673433</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1420623931329175</v>
+        <v>-0.1430507625197919</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1873229384724553</v>
+        <v>-0.1883078166345626</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2723942922636482</v>
+        <v>-0.2828239279618003</v>
       </c>
     </row>
     <row r="11">
@@ -2477,46 +2477,46 @@
         <v>3795</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2338481993481736</v>
+        <v>-0.2350531463735948</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3862208687852728</v>
+        <v>-0.3874252975340653</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.5829510919264465</v>
+        <v>-0.5841139814149798</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5437006073473896</v>
+        <v>-0.5448712880035558</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5419256291266024</v>
+        <v>-0.5431104132589155</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2564894469770778</v>
+        <v>-0.2577427414606106</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.06376155442369225</v>
+        <v>-0.06506824907016551</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1480464064962277</v>
+        <v>-0.1493428912783656</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1419018804894563</v>
+        <v>-0.143202120715074</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.003066933332426913</v>
+        <v>-0.004424992103622571</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.04404238250764081</v>
+        <v>0.04266626966568765</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1175369253172533</v>
+        <v>-0.1188703273804492</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1688850803991713</v>
+        <v>-0.1553290340475684</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2090188205866568</v>
+        <v>-0.2194484562848089</v>
       </c>
     </row>
     <row r="12">
@@ -2529,566 +2529,566 @@
         <v>3667</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.2355493104167152</v>
+        <v>-0.2372391200094697</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.5812024093646997</v>
+        <v>-0.5828529397026472</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.6893199429825785</v>
+        <v>-0.6909551410062775</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.8166735185981153</v>
+        <v>-0.8182705748900645</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.8503145174424631</v>
+        <v>-0.8519213101829024</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.6198685660507479</v>
+        <v>-0.6215290298376672</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.3629154336722138</v>
+        <v>-0.3646496220489723</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.433714960808004</v>
+        <v>-0.4354464335127091</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.2616917256872071</v>
+        <v>-0.2634730445305067</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.006018756348879606</v>
+        <v>-0.007899242168086573</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.01988034355164814</v>
+        <v>-0.006423049841430384</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1491186751617661</v>
+        <v>-0.1356663864416561</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1330493155585444</v>
+        <v>-0.1194932692069415</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1014899685563151</v>
+        <v>-0.1119196042544672</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.09303</t>
+          <t>X &gt; -0.09304</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>3530</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.02210718572558079</v>
+        <v>0.01979038370696173</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1044464822270967</v>
+        <v>-0.1067996928463444</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2295186488206014</v>
+        <v>-0.2318551311974346</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.33851010970929</v>
+        <v>-0.3408112606924618</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.635270001239455</v>
+        <v>-0.6375121752862896</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1526390517148499</v>
+        <v>-0.1550058803024257</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1744216726133274</v>
+        <v>0.1719572837848986</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.260868905996773</v>
+        <v>0.2583581279741836</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3005555333574037</v>
+        <v>0.2980295259739805</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.555246212352138</v>
+        <v>0.5686513400049691</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.5771217832186863</v>
+        <v>0.5905790769289041</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.5548477167680872</v>
+        <v>0.5683000054881973</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5595222842934433</v>
+        <v>0.5730783306450462</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.4976288856915474</v>
+        <v>0.4871992499933953</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.07183</t>
+          <t>X &gt; -0.07184</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>3359</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2241143973427455</v>
+        <v>0.2209842069953325</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.4107337590420457</v>
+        <v>0.4074523759563249</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.3292426886095683</v>
+        <v>0.3259607162457101</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.2974355130507149</v>
+        <v>0.2941688714907116</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2247302565798321</v>
+        <v>-0.2278748976465153</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.2376977960869482</v>
+        <v>0.2344313541176817</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.6750849668184173</v>
+        <v>0.6716817310925478</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.7005713375216303</v>
+        <v>0.6971313723336507</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.8645976779657261</v>
+        <v>0.8611035236274205</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.086220036849681</v>
+        <v>1.099625164502513</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.179174363618735</v>
+        <v>1.192631657328953</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.886079104768875</v>
+        <v>0.899531393488985</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.091010561105897</v>
+        <v>1.1045666074575</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.043024242295552</v>
+        <v>1.032594606597399</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.05063</t>
+          <t>X &gt; -0.05064</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>3146</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.2499806458540945</v>
+        <v>0.245780228184735</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.653871315556728</v>
+        <v>0.6494138928940529</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.72068426026091</v>
+        <v>0.7161721769259657</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.4875153499795388</v>
+        <v>0.4830850531976978</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.2205635356241373</v>
+        <v>0.2161731932505617</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3449205344128217</v>
+        <v>0.3405116913235986</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.9131755452368111</v>
+        <v>0.9085770866888012</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6226000663685411</v>
+        <v>0.6180546301706329</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.7205321573000347</v>
+        <v>0.7337308962547979</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.173649184605232</v>
+        <v>1.187054312258063</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.286759814515236</v>
+        <v>1.300217108225453</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.193997390169628</v>
+        <v>1.207449678889738</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.473043478525426</v>
+        <v>1.486599524877029</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.500260042842406</v>
+        <v>1.489830407144254</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.02942</t>
+          <t>X &gt; -0.02944</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2853</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.3037644769928249</v>
+        <v>0.2978326587351319</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.7043619737862485</v>
+        <v>0.6981076666116053</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8185238388855822</v>
+        <v>0.8121821054977829</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.7231271305685638</v>
+        <v>0.7168295918481604</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1339680844872007</v>
+        <v>0.1278132196963284</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.3806366480546046</v>
+        <v>0.3744249072927488</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.12105753604952</v>
+        <v>1.114573388235165</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.8837431867029366</v>
+        <v>0.8772864009430705</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.103149890075493</v>
+        <v>1.116348629030256</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.374651063266988</v>
+        <v>1.388056190919819</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.275050210032475</v>
+        <v>1.288507503742693</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.379535014766617</v>
+        <v>1.392987303486727</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.800500172486288</v>
+        <v>1.814056218837891</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.699713267819</v>
+        <v>1.689283632120848</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.008221</t>
+          <t>X &gt; -0.008234</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2494</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.9679462336115563</v>
+        <v>0.9590839694656452</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.139183423110801</v>
+        <v>1.129986711936027</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.006727289744596</v>
+        <v>0.9975140016547854</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.079090441554627</v>
+        <v>1.069863449412161</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.6831336424939707</v>
+        <v>0.673972338549703</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.9805755802096314</v>
+        <v>0.9936184765039968</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.760152681848631</v>
+        <v>1.750591483971291</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.774124054518616</v>
+        <v>1.787305063813854</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.993797785016341</v>
+        <v>2.006996523971104</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.30646329766283</v>
+        <v>2.319868425315661</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.181902435253832</v>
+        <v>2.19535972896405</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.456862978325013</v>
+        <v>2.470315267045123</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.517763138831583</v>
+        <v>2.531319185183186</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.607099547290716</v>
+        <v>2.596669911592564</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.01298</t>
+          <t>X &gt; 0.01297</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.578531376759727</v>
+        <v>1.587201282616071</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.171634206096257</v>
+        <v>2.178603034944175</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.345216470603411</v>
+        <v>2.378656794677077</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.928950691888808</v>
+        <v>2.935018301901806</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.133203055858388</v>
+        <v>2.13964284954826</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.478060830463569</v>
+        <v>2.511440851111026</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.199396340313157</v>
+        <v>3.232417695636329</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.25378714731638</v>
+        <v>3.286676066067599</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.097955587355038</v>
+        <v>3.130907179687</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.338394650786107</v>
+        <v>3.371035776722074</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.038809652689473</v>
+        <v>3.071547888604059</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.97836113625587</v>
+        <v>3.011139311101566</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.032264894206172</v>
+        <v>3.064922107077251</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.281986226482459</v>
+        <v>3.290657757303784</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.03418</t>
+          <t>X &gt; 0.03417</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1729</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.752662199720696</v>
+        <v>1.765184489396319</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.029592341811323</v>
+        <v>3.042502151387374</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.69249371031583</v>
+        <v>2.705500841733432</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.087019891680605</v>
+        <v>3.066806285726187</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.581829820274628</v>
+        <v>2.561709480983374</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.705761058163802</v>
+        <v>2.718803954458167</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.315070140197477</v>
+        <v>3.328136394497953</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.657603340606265</v>
+        <v>3.670784349901503</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.844723755175835</v>
+        <v>2.857922494130598</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.324847268817663</v>
+        <v>3.338252396470494</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.177930844442251</v>
+        <v>3.191388138152469</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.923129502076868</v>
+        <v>2.936581790796978</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.965570090669267</v>
+        <v>2.97912613702087</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.215291422945555</v>
+        <v>3.204861787247403</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.05539</t>
+          <t>X &gt; 0.05537</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.956456564162835</v>
+        <v>1.930848675347995</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.147966342929486</v>
+        <v>3.120783030463443</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.243637229885799</v>
+        <v>3.216207724139771</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.344257485824052</v>
+        <v>3.346432867728133</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.665583816333935</v>
+        <v>2.638348697416248</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.542268390795734</v>
+        <v>2.515260218291701</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.719806763285028</v>
+        <v>3.691937385304449</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.883759409384318</v>
+        <v>3.855562504657151</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.472128387157134</v>
+        <v>3.444194924168016</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.463517928636918</v>
+        <v>3.435201145357425</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.258764604319339</v>
+        <v>3.230499987097232</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.29314776166477</v>
+        <v>3.264878139452556</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.083271832346803</v>
+        <v>3.054958540518967</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.33299316462309</v>
+        <v>3.2806941907455</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.07659</t>
+          <t>X &gt; 0.07657</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1162</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.584014347604132</v>
+        <v>2.596536637279755</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.640254848237134</v>
+        <v>3.653164657813186</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4.192029859368589</v>
+        <v>4.205036990786191</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4.236224472182634</v>
+        <v>4.249203614581099</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3.697803257110465</v>
+        <v>3.710914061485404</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.306777036478451</v>
+        <v>3.319819932772816</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.771096675488444</v>
+        <v>4.78416292978892</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.992381435054618</v>
+        <v>5.005562444349856</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>4.587147469698472</v>
+        <v>4.600346208653235</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>4.425490443018219</v>
+        <v>4.43889557067105</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4.22073711870064</v>
+        <v>4.234194412410858</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>4.513295835426455</v>
+        <v>4.526748124146565</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.609392343242313</v>
+        <v>4.622948389593915</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.773055155725139</v>
+        <v>4.762625520026987</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.09779</t>
+          <t>X &gt; 0.09777</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>956</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.573507286484585</v>
+        <v>3.586029576160207</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.413816518708614</v>
+        <v>5.426726328284666</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>6.064972916714531</v>
+        <v>6.077980048132133</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6.509033580702784</v>
+        <v>6.522012723101248</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>5.552202323789615</v>
+        <v>5.565313128164554</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>4.908221667363016</v>
+        <v>4.921264563657381</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>6.392525606994504</v>
+        <v>6.40559186129498</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>6.134547229133503</v>
+        <v>6.147728238428741</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>6.073547342951201</v>
+        <v>6.086746081905964</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>6.374049772986034</v>
+        <v>6.387454900638865</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>5.541681385906948</v>
+        <v>5.555138679617166</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>5.889872074633139</v>
+        <v>5.903324363353249</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>5.992630015989484</v>
+        <v>6.006186062341087</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>6.033146327345271</v>
+        <v>6.022716691647119</v>
       </c>
     </row>
     <row r="23">
@@ -3098,49 +3098,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.022852406607065</v>
+        <v>4.089797361205328</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>5.794737440259354</v>
+        <v>5.85783529817904</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>6.903628132159007</v>
+        <v>6.964941260107359</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>7.785760964014621</v>
+        <v>7.720948631480454</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>6.871399899318398</v>
+        <v>6.932346187270866</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>7.294155120242074</v>
+        <v>7.354876662462893</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>8.462554235049993</v>
+        <v>8.521730758766189</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>8.120684119476522</v>
+        <v>8.05466211497945</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>8.184997516502236</v>
+        <v>8.118836404013614</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>7.961438747514407</v>
+        <v>8.01985628102544</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>6.628865874324646</v>
+        <v>6.688747112752729</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.663249031670077</v>
+        <v>6.723125265108052</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>6.869560836765274</v>
+        <v>6.928756639579376</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>6.743342319417501</v>
+        <v>6.779022953135069</v>
       </c>
     </row>
     <row r="24">
@@ -3150,49 +3150,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.247302420530758</v>
+        <v>4.175888703193451</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.709802881640584</v>
+        <v>4.783637521372235</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.351971212081033</v>
+        <v>5.424369095197079</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.51926138172557</v>
+        <v>6.590097197365317</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>6.277136462949699</v>
+        <v>6.347665632435309</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>7.167170993257947</v>
+        <v>7.23675563840176</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.56391875746715</v>
+        <v>8.631335219963987</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>8.393031654981947</v>
+        <v>8.460124564342934</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>8.628328065095936</v>
+        <v>8.695000395985836</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.63005473191987</v>
+        <v>7.69715260557313</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.536412518713391</v>
+        <v>6.604877482815901</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>6.867091972355119</v>
+        <v>6.935113623336896</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7.632022546595401</v>
+        <v>7.698394722686217</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.696558693686505</v>
+        <v>6.74069842025002</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>588</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.309282768225394</v>
+        <v>4.321805057901017</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.908593509002642</v>
+        <v>4.921503318578694</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.044337047304012</v>
+        <v>6.057344178721614</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6.684794261544155</v>
+        <v>6.69777340394262</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>6.316441073682874</v>
+        <v>6.329551878057813</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>6.954019065820304</v>
+        <v>6.96706196211467</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>8.569965620656873</v>
+        <v>8.583031874957349</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>9.123190385140681</v>
+        <v>9.136371394435919</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>9.912530635012793</v>
+        <v>9.925729373967556</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>8.212065313930452</v>
+        <v>8.225470441583283</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7.837243962401985</v>
+        <v>7.850701256112202</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>8.381831201380066</v>
+        <v>8.395283490100176</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>8.981984753700466</v>
+        <v>8.995540800052069</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.701093841078801</v>
+        <v>7.690664205380649</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>496</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>5.772690712048089</v>
+        <v>5.785213001723712</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.572407421664479</v>
+        <v>5.585317231240531</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.790441940874338</v>
+        <v>6.80344907229194</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7.928759589610863</v>
+        <v>7.941738732009327</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.785499664861284</v>
+        <v>6.798610469236223</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>8.091006118705984</v>
+        <v>8.104049015000349</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.619175627240146</v>
+        <v>9.632241881540622</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>10.16005674458767</v>
+        <v>10.17323775388291</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>10.9055084713086</v>
+        <v>10.91870721026336</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>10.25699618950648</v>
+        <v>10.27040131715931</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>10.45546867164052</v>
+        <v>10.46892596535073</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>11.69952924834078</v>
+        <v>11.71298153706089</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>12.08572625029911</v>
+        <v>12.09928229665071</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>10.11770564709153</v>
+        <v>10.10727601139337</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>419</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>5.74045189458716</v>
+        <v>5.752974184262783</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.606205250596652</v>
+        <v>4.619115060172703</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.836634873355663</v>
+        <v>6.849642004773266</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7.921541943910668</v>
+        <v>7.934521086309132</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.18980330640413</v>
+        <v>6.202914110779069</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.441899182067282</v>
+        <v>7.454942078361647</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9.02780985620312</v>
+        <v>9.040876110503596</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>9.753943879855989</v>
+        <v>9.767124889151226</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>10.64759793162118</v>
+        <v>10.66079667057595</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>9.797472746593257</v>
+        <v>9.810877874246088</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>10.30870987573628</v>
+        <v>10.3221671694465</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>11.77507394000297</v>
+        <v>11.78852622872308</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>11.59348281354493</v>
+        <v>11.60703885989653</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>10.64988672338686</v>
+        <v>10.6394570876887</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>350</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.22084739407574</v>
+        <v>5.233369683751363</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.609273781111483</v>
+        <v>3.622183590687534</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.928690788800608</v>
+        <v>6.941697920218211</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.487515349979532</v>
+        <v>8.500494492377996</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.234808420621654</v>
+        <v>6.247919224996593</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>7.675107501194461</v>
+        <v>7.688150397488826</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>9.30465949820789</v>
+        <v>9.317725752508366</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>9.980333242283542</v>
+        <v>9.99351425157878</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>11.06219049895837</v>
+        <v>11.07538923791313</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.640636742501869</v>
+        <v>9.6540418701547</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.57874056104144</v>
+        <v>10.59219785475166</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>10.32740943267258</v>
+        <v>10.34086172139269</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>11.05001196458483</v>
+        <v>11.06356801093644</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>10.15687615400397</v>
+        <v>10.14644651830582</v>
       </c>
     </row>
     <row r="29">
@@ -3410,49 +3410,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.506561679790032</v>
+        <v>3.33303745783774</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.561654733492432</v>
+        <v>2.386303192016442</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.166786026895849</v>
+        <v>4.98156502985276</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7.963705826170006</v>
+        <v>7.769597482411221</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>5.091951277764508</v>
+        <v>4.905726533966693</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.389393215480169</v>
+        <v>5.535326477223045</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>7.971326164874561</v>
+        <v>8.108423426926969</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>9.170809432759718</v>
+        <v>9.302484351246541</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>10.44314287991075</v>
+        <v>10.57040584920881</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.92635102821616</v>
+        <v>10.05271296650022</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.05493103723191</v>
+        <v>10.18023772186129</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>9.089314194577341</v>
+        <v>9.217938133352824</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.12669093452448</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.585447582575398</v>
+        <v>8.69129701664469</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>243</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.239071967855864</v>
+        <v>2.251594257531487</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.6274983548916069</v>
+        <v>0.640408164467658</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.347855985743578</v>
+        <v>4.36086311716118</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.947244920820218</v>
+        <v>6.960224063218682</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.174255804513486</v>
+        <v>5.187366608888425</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.471697742229146</v>
+        <v>5.484740638523512</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.798486658701719</v>
+        <v>5.811552913002195</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>8.623484329879062</v>
+        <v>8.6366653391743</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>10.62009761242104</v>
+        <v>10.6332963513758</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>10.18149506113797</v>
+        <v>10.1949001887908</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>9.976741736820387</v>
+        <v>9.990199030530604</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>9.188079626676114</v>
+        <v>9.201531915396224</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.01594896331737</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.371455813028071</v>
+        <v>7.361026177329919</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>196</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.098398414483903</v>
+        <v>2.110920704159525</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.418247986709595</v>
+        <v>-0.4052408552919928</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.283433717326474</v>
+        <v>3.296412859724938</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.7041961757236948</v>
+        <v>0.717306980098634</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.022046276704657</v>
+        <v>2.035089172999022</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.937312559432378</v>
+        <v>1.950378813732854</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.531353650446803</v>
+        <v>4.544534659742041</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.531578254060413</v>
+        <v>7.544776993015176</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.212065313930452</v>
+        <v>8.225470441583283</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.497107907980215</v>
+        <v>7.510565201690433</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.000878820427687</v>
+        <v>6.014331109147797</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.111236454380744</v>
+        <v>7.124792500732347</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.279325133595812</v>
+        <v>3.26889549789766</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>151</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1755575255079904</v>
+        <v>-0.1630352358323677</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-3.773886105359658</v>
+        <v>-3.760976295783607</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.519748189439696</v>
+        <v>-1.506741058022094</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.246266532571774</v>
+        <v>3.259245674970238</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.05883869498305216</v>
+        <v>0.07194949935799144</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.680783943956989</v>
+        <v>1.693826840251354</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.9337985710555685</v>
+        <v>0.9468648253560445</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.115621794790627</v>
+        <v>3.128802804085865</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.365880186754026</v>
+        <v>6.379078925708789</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.515755001726099</v>
+        <v>5.52916012937893</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.973253333037647</v>
+        <v>5.986710626747865</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.020881523495667</v>
+        <v>4.034333812215777</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>3.600626912550766</v>
+        <v>3.614182958902369</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.123161688947782</v>
+        <v>-0.1335913246459342</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>123</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.978106395237177</v>
+        <v>1.990628684912799</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-2.072491607970974</v>
+        <v>-2.059581798394923</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.8413440544049635</v>
+        <v>-0.8283369229873614</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.166957858690331</v>
+        <v>4.179937001088796</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.249512136869633</v>
+        <v>-1.236401332494694</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.6739460610086283</v>
+        <v>0.6869889573029937</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.5892123437363495</v>
+        <v>0.6022785980368255</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.374061465280043</v>
+        <v>3.387242474575281</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>7.378102229504243</v>
+        <v>7.391300968459007</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.527977044476316</v>
+        <v>6.541382172129147</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.949239980321352</v>
+        <v>7.962697274031569</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.357606877504168</v>
+        <v>6.371059166224278</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>4.311336006396672</v>
+        <v>4.324892052748275</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.496016688266451</v>
+        <v>0.4855870525682988</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>103</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.846367505032738</v>
+        <v>2.858889794708361</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-1.677827467154813</v>
+        <v>-1.664917657578762</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.101822387343638</v>
+        <v>-1.088815255926036</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.882799677302692</v>
+        <v>3.895778819701157</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-2.480864256216073</v>
+        <v>-2.467753451841133</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.212548532092647</v>
+        <v>-1.199505635798282</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.297282249364926</v>
+        <v>-1.28421599506445</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.148155711076875</v>
+        <v>1.161336720372113</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.941524756933404</v>
+        <v>5.954723495888167</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.091399571905477</v>
+        <v>5.104804699558308</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.828393820403441</v>
+        <v>6.841851114113659</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.950155618525564</v>
+        <v>3.963607907245674</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>2.55902722117289</v>
+        <v>2.572583267524493</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-1.074746592181889</v>
+        <v>-1.085176227880041</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.268466441694791</v>
+        <v>2.280988731370414</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-1.724059552221846</v>
+        <v>-1.711149742645794</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.2620241221339441</v>
+        <v>0.2750312535515462</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5.154182016646203</v>
+        <v>5.167161159044667</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-3.717572531759302</v>
+        <v>-3.704461727384363</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-4.69534050179211</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.4006191386688442</v>
+        <v>-0.3874381293736064</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1.919333356101227</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>1.08261329872613</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>4.435883418184289</v>
+        <v>4.449340711894507</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>0.9122902928212611</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.7118927973199334</v>
+        <v>-0.6983367509683305</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-4.033600036472215</v>
+        <v>-4.044029672170367</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that ROC-14 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that ROC-14 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,53 +3904,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.2415</t>
+          <t>X &lt; -0.2414</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.41132358455193</v>
+        <v>9.423845874227553</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.609273781111476</v>
+        <v>6.622183590687527</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.595357455467273</v>
+        <v>8.608364586884875</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14.67799154045573</v>
+        <v>14.69097068285419</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>12.94909413490737</v>
+        <v>12.96220493928231</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.675107501194461</v>
+        <v>9.688150397488826</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>7.209421402969795</v>
+        <v>7.222487657270271</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.980333242283528</v>
+        <v>1.993514251578766</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.652095215327343</v>
+        <v>-1.63889647637258</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.692696590831453</v>
+        <v>-3.679291463178622</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.087926105625229</v>
+        <v>-5.074468811915011</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.672590567327418</v>
+        <v>-2.659138278607308</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-4.283321368748503</v>
+        <v>-4.2697653223969</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-4.033600036472215</v>
+        <v>-4.044029672170367</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>110</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.506561679790025</v>
+        <v>7.519083969465647</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.167715339553041</v>
+        <v>3.180625149129092</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.227392087501912</v>
+        <v>8.240399218919514</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>15.63037249283668</v>
+        <v>15.64335163523514</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>10.54649673230996</v>
+        <v>10.5596075366849</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.207575033661982</v>
+        <v>7.220617929956347</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.031932225480624</v>
+        <v>8.0449984797811</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.6170693551190709</v>
+        <v>-0.6038883458238331</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.587160150392272</v>
+        <v>-1.573961411437509</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.5281944263293</v>
+        <v>-1.514789298676469</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.642038659737779</v>
+        <v>-2.628581366027561</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.119617224880372</v>
+        <v>0.133069513600482</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.11881920424635</v>
+        <v>-2.105263157894747</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.9600069628791488</v>
+        <v>-0.9704365985773009</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>150</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.173228346456696</v>
+        <v>8.185750636132319</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.561654733492439</v>
+        <v>6.57456454306849</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.500119360229178</v>
+        <v>9.51312649164678</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>12.96370582617001</v>
+        <v>12.97668496856847</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>12.42528461109784</v>
+        <v>12.43839541547278</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.722726548813498</v>
+        <v>6.735769445107863</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.637992831541219</v>
+        <v>6.651059085841695</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.170809432759725</v>
+        <v>2.183990442054963</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.776476213244095</v>
+        <v>0.7896749521988582</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.259684361549496</v>
+        <v>1.273089489202327</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.388264370565246</v>
+        <v>2.401721664275463</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.422647527910684</v>
+        <v>4.436099816630794</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.669059583632439</v>
+        <v>4.682615629984042</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>4.918780915908727</v>
+        <v>4.908351280210574</v>
       </c>
     </row>
     <row r="9">
@@ -4067,46 +4067,46 @@
         <v>207</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4.028300810224806</v>
+        <v>4.040823099900429</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.866002559579393</v>
+        <v>3.878912369155444</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.403501002741251</v>
+        <v>5.416508134158853</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.949213072546819</v>
+        <v>7.962192214945283</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>7.410791857474649</v>
+        <v>7.423902661849588</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.360407708233794</v>
+        <v>3.373450604528159</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.275673990961515</v>
+        <v>3.288740245261991</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.359215229861171</v>
+        <v>1.372396239156409</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.298215343678869</v>
+        <v>1.311414082633632</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.897365520969785</v>
+        <v>1.910770648622616</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.209520409212594</v>
+        <v>1.222977702922812</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.176270716316473</v>
+        <v>3.189723005036583</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.205291467690422</v>
+        <v>4.218847514042025</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.971921012527091</v>
+        <v>3.961491376828938</v>
       </c>
     </row>
     <row r="10">
@@ -4116,49 +4116,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>3.889540403194275</v>
+        <v>3.902062692869897</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.46945615193215</v>
+        <v>5.482365961508201</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7.202247019803643</v>
+        <v>7.215254151221245</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7.332500152411143</v>
+        <v>7.345479294809607</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.375639221026915</v>
+        <v>5.388750025401855</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.900031513352509</v>
+        <v>3.913074409646875</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.106077937924205</v>
+        <v>3.119144192224681</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.929674680986672</v>
+        <v>1.94285569028191</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.514064865726361</v>
+        <v>1.527263604681124</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.082379397010484</v>
+        <v>2.095784524663316</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.232236001770922</v>
+        <v>2.245693295481139</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.03966880450642</v>
+        <v>4.05312109322653</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.683243980795567</v>
+        <v>4.696800027147169</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>5.507155767628781</v>
+        <v>5.63175553552972</v>
       </c>
     </row>
     <row r="11">
@@ -4168,49 +4168,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.493084590841242</v>
+        <v>2.505606880516865</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.194179441488842</v>
+        <v>5.207089251064893</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.686103187722438</v>
+        <v>6.69911031914004</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6.546814541354195</v>
+        <v>6.559793683752659</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>6.547476884233518</v>
+        <v>6.560587688608457</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.879959253216015</v>
+        <v>3.89300214951038</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.177974862089293</v>
+        <v>2.191041116389769</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.788958579210757</v>
+        <v>2.802139588505995</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2.997500472004198</v>
+        <v>3.010699210958961</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.608291729024778</v>
+        <v>1.621696856677609</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.13399662573147</v>
+        <v>1.147453919441688</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.785630456931344</v>
+        <v>2.799082745651454</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>3.187557229265266</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.477046498564562</v>
+        <v>3.575017946877246</v>
       </c>
     </row>
     <row r="12">
@@ -4220,569 +4220,569 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.797978845458687</v>
+        <v>1.810501135134309</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.176425192574271</v>
+        <v>5.189335002150322</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.579959679590452</v>
+        <v>5.592966811008054</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.708216804213926</v>
+        <v>6.72119594661239</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6.968198782754534</v>
+        <v>6.981309587129473</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.469233534841443</v>
+        <v>5.482276431135809</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.787693430343623</v>
+        <v>3.800759684644099</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.118913225174893</v>
+        <v>4.132094234470131</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.059909346976617</v>
+        <v>3.073108085931381</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.21178016993273</v>
+        <v>1.225185297585561</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.321597703898576</v>
+        <v>1.220084937728558</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.273014929380288</v>
+        <v>2.169433149964121</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.171067615760954</v>
+        <v>2.066717166390198</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.734340942736367</v>
+        <v>1.807949673784876</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.09303</t>
+          <t>X &lt; -0.09304</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.0677732184885329</v>
+        <v>-0.05525092881291016</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.294049099689616</v>
+        <v>1.306958909265667</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.681653006551556</v>
+        <v>1.694660137969159</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.437884229925878</v>
+        <v>2.450863372324342</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.090386332537591</v>
+        <v>4.10349713691253</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.570926861802548</v>
+        <v>1.583969758096913</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.07875208238679221</v>
+        <v>-0.06568582808631618</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.7024300038599947</v>
+        <v>-0.6892489945647569</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.7634298900422962</v>
+        <v>-0.750231151087533</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.155153673978191</v>
+        <v>-2.226128038184214</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.275262578675992</v>
+        <v>-2.346449704585552</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.155968824290582</v>
+        <v>-2.227427132610451</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.176084773322941</v>
+        <v>-2.248201980078846</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.998148631935649</v>
+        <v>-1.936793076744806</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.07183</t>
+          <t>X &lt; -0.07184</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.8885000486050387</v>
+        <v>-0.875977758929416</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.142048970211263</v>
+        <v>-1.129139160635212</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.043090516314038</v>
+        <v>-1.030083384896436</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.7893805935830827</v>
+        <v>-0.7764014511846185</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.388247574060806</v>
+        <v>1.401358378435745</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4130759203222993</v>
+        <v>-0.4000330240279339</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.102747909199522</v>
+        <v>-2.089681654899046</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.323017727734111</v>
+        <v>-2.309836718438874</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.877844774410228</v>
+        <v>-2.864646035455465</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.786875176975435</v>
+        <v>-3.83802162190878</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.174441900061815</v>
+        <v>-4.22538999621073</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.96025210034211</v>
+        <v>-3.012745067857658</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.810675734812556</v>
+        <v>-3.862613614129955</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.743744964008457</v>
+        <v>-3.695453517142603</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.05063</t>
+          <t>X &lt; -0.05064</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.7356258202099752</v>
+        <v>-0.7231035305343525</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.565949433174232</v>
+        <v>-1.553039623598181</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.960818139770822</v>
+        <v>-1.94781100835322</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.146971257163322</v>
+        <v>-1.133992114764858</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3182049722354918</v>
+        <v>-0.3050941678605525</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.6067005345198311</v>
+        <v>-0.5936576382254657</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.25393425179211</v>
+        <v>-2.240867997491634</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.451586400573611</v>
+        <v>-1.438405391278373</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.655586347850736</v>
+        <v>-1.694700047801149</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.040380870022588</v>
+        <v>-3.078816669155451</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.389078104132764</v>
+        <v>-3.427371616872612</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.1067642367952</v>
+        <v>-3.145356272171036</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.965549510250447</v>
+        <v>-4.003658879819874</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.155220393848971</v>
+        <v>-4.118799521228738</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.02942</t>
+          <t>X &lt; -0.02944</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.6331497856617574</v>
+        <v>-0.6206274959861346</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.181701378884185</v>
+        <v>-1.168791569308134</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.576570085480775</v>
+        <v>-1.563562954063173</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.294456664338718</v>
+        <v>-1.281477521940253</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.01055441699631388</v>
+        <v>0.002556387378625402</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4724139219533967</v>
+        <v>-0.4593710256590313</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.999820380303881</v>
+        <v>-1.986754126003405</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.555842047878095</v>
+        <v>-1.542661038582857</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.956046583108495</v>
+        <v>-1.983293916442001</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.537527298780041</v>
+        <v>-2.564803114647731</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.321020256527596</v>
+        <v>-2.348595192505272</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.55018821720229</v>
+        <v>-2.577598813506199</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.463054237505773</v>
+        <v>-3.490017017896122</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.325307566166025</v>
+        <v>-3.299982053122754</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.008221</t>
+          <t>X &lt; -0.008234</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.420732718302943</v>
+        <v>-1.408210428627321</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.423247928406646</v>
+        <v>-1.410338118830595</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.341358589711227</v>
+        <v>-1.328351458293625</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.389889724088235</v>
+        <v>-1.376910581689771</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.7960105815918652</v>
+        <v>-0.7828997772169259</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.18186498368501</v>
+        <v>-1.200662815519863</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.280313668160623</v>
+        <v>-2.267247413860147</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.35822795785284</v>
+        <v>-2.376534304516298</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.626508861382781</v>
+        <v>-2.644692589567256</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.086791146216335</v>
+        <v>-3.105019963533998</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.901235529813313</v>
+        <v>-2.919664237755597</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.313397129186612</v>
+        <v>-3.331582988708924</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.402753701825368</v>
+        <v>-3.421052631578945</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.600181159939574</v>
+        <v>-3.582372837084449</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.01298</t>
+          <t>X &lt; 0.01297</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>2055</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.597554542970258</v>
+        <v>-1.608823007278538</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.998474402907895</v>
+        <v>-2.008768790264845</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.271198469228182</v>
+        <v>-2.306640950213684</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.819239910264095</v>
+        <v>-2.829745795690698</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.001071978049438</v>
+        <v>-2.010788620720469</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.308134656550848</v>
+        <v>-2.343564857687412</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.99795931847494</v>
+        <v>-3.033389669412102</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.10041812667744</v>
+        <v>-3.135757253238587</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.893426699377279</v>
+        <v>-2.928771649742892</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.135329399175781</v>
+        <v>-3.170491537185896</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.82845088696633</v>
+        <v>-2.863584458173513</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.768083309878982</v>
+        <v>-2.803245508276028</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.821861298339023</v>
+        <v>-2.856943384283142</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.129880884577886</v>
+        <v>-3.140310520276039</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.03418</t>
+          <t>X &lt; 0.03417</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.226063013586923</v>
+        <v>-1.234491837645102</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.957772669370556</v>
+        <v>-1.96618225442402</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.799389641407487</v>
+        <v>-1.80793690303625</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.037385281304076</v>
+        <v>-2.024406138905611</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.675642830255129</v>
+        <v>-1.662532025880189</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.72481063224803</v>
+        <v>-1.733406768749191</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.115487921939526</v>
+        <v>-2.123944325264866</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.397263761286439</v>
+        <v>-2.405690147625627</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.780900835936237</v>
+        <v>-1.789595838460713</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.117109406388181</v>
+        <v>-2.125817614622818</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.012610663615767</v>
+        <v>-2.021402566966849</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.832857874906992</v>
+        <v>-1.841723535843919</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.861318084676256</v>
+        <v>-1.870249915085026</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.081903546788055</v>
+        <v>-2.073586322416681</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.05539</t>
+          <t>X &lt; 0.05537</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>2738</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-1.00252922930089</v>
+        <v>-0.9900069396252675</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.467689270387766</v>
+        <v>-1.454779460811714</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.588672488387992</v>
+        <v>-1.57566535697039</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.603979763349642</v>
+        <v>-1.608195507101946</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.249512136869633</v>
+        <v>-1.236401332494694</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.151029217149109</v>
+        <v>-1.137986320854743</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.726305893413233</v>
+        <v>-1.713239639112757</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.846197369961367</v>
+        <v>-1.833016360666129</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.596108547966267</v>
+        <v>-1.582909809011504</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.5878721665322</v>
+        <v>-1.574467038879369</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.480883142507842</v>
+        <v>-1.467425848797625</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.499493591310731</v>
+        <v>-1.486041302590621</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.388625702968504</v>
+        <v>-1.375069656616901</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.556992154458939</v>
+        <v>-1.530898780661104</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.07659</t>
+          <t>X &lt; 0.07657</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.9843172588501119</v>
+        <v>-0.9888735902160519</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.251660904640723</v>
+        <v>-1.256281228075792</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.529419305552437</v>
+        <v>-1.533986978824359</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.514381823232384</v>
+        <v>-1.518945079003167</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.304594720242804</v>
+        <v>-1.309280547342631</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.12223469149658</v>
+        <v>-1.126956116720983</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.654463133895796</v>
+        <v>-1.659018433538151</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.771566453765104</v>
+        <v>-1.77612919902181</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.582020627460935</v>
+        <v>-1.586654835035191</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.516097408244256</v>
+        <v>-1.52083579624275</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.436472179628872</v>
+        <v>-1.441259040980682</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.550277460993001</v>
+        <v>-1.555026084644858</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.586018671445814</v>
+        <v>-1.590797596824657</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.684372537344657</v>
+        <v>-1.679727307868006</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.09779</t>
+          <t>X &lt; 0.09777</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3208</v>
+        <v>3209</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.049787280160302</v>
+        <v>-1.053231362626214</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.465260380379199</v>
+        <v>-1.468693244368133</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.719514066300803</v>
+        <v>-1.72289835307371</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.821460944080656</v>
+        <v>-1.824806177750261</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.535341230783828</v>
+        <v>-1.538816103068754</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.314586884022319</v>
+        <v>-1.318110981790902</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.724889490905646</v>
+        <v>-1.728294147989146</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.677769700200244</v>
+        <v>-1.681224695321923</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.628752544925845</v>
+        <v>-1.632229217060633</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.714993928197295</v>
+        <v>-1.718507149453139</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.466817120143773</v>
+        <v>-1.470424454445997</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.571121942494308</v>
+        <v>-1.574696404691743</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.600390920158979</v>
+        <v>-1.603988731386664</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.645225734132829</v>
+        <v>-1.641560426447775</v>
       </c>
     </row>
     <row r="23">
@@ -4795,46 +4795,46 @@
         <v>3366</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.9397242036074331</v>
+        <v>-0.95679646853376</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.233490322753866</v>
+        <v>-1.250183828749158</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.553478507700945</v>
+        <v>-1.570083458012682</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.733371582992703</v>
+        <v>-1.720392440594239</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.515456129642899</v>
+        <v>-1.531974954897585</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.587488823642531</v>
+        <v>-1.604084338729315</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.834385862005568</v>
+        <v>-1.850966806044852</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.781740982424147</v>
+        <v>-1.768559973128909</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.767575996782611</v>
+        <v>-1.754377257827848</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.711631167629534</v>
+        <v>-1.727899630481154</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.395647769535671</v>
+        <v>-1.411872874163237</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.404351680323678</v>
+        <v>-1.420590603005003</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.451918537345676</v>
+        <v>-1.468062520694104</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.453173926634342</v>
+        <v>-1.463603562332494</v>
       </c>
     </row>
     <row r="24">
@@ -4847,46 +4847,46 @@
         <v>3489</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.8086867496788486</v>
+        <v>-0.7961644600032258</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7773912533684708</v>
+        <v>-0.7930447114302339</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.9570234969136777</v>
+        <v>-0.9725877940675076</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.154423163065012</v>
+        <v>-1.17002361483631</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.105876052138285</v>
+        <v>-1.121353012200174</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.250583907768331</v>
+        <v>-1.266136950850573</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.491679174560986</v>
+        <v>-1.507217039253646</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.4858429277553</v>
+        <v>-1.501274221750478</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.50285979133519</v>
+        <v>-1.518281544652893</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.306972762221861</v>
+        <v>-1.32219632051234</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.095126236536693</v>
+        <v>-1.110305827133466</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.15951613102181</v>
+        <v>-1.174708929669222</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.30610756058914</v>
+        <v>-1.321204809366471</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.155165773687138</v>
+        <v>-1.16559540938529</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3576</v>
+        <v>3577</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.6962803374849784</v>
+        <v>-0.6981862255204234</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.6769182876892827</v>
+        <v>-0.6788951021437342</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.9174998201443927</v>
+        <v>-0.9194264626453048</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9953943783289603</v>
+        <v>-0.9972951448038856</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.9331533247459518</v>
+        <v>-0.9350940807161052</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.01127642737697</v>
+        <v>-1.013184529787523</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.248508238325741</v>
+        <v>-1.250354604634495</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.365762314867304</v>
+        <v>-1.367595752009606</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.467589690134851</v>
+        <v>-1.469398191296406</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.18538081535926</v>
+        <v>-1.187303324723018</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.123331047149193</v>
+        <v>-1.125280197921931</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.213275706671027</v>
+        <v>-1.215199428968539</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.310625441062363</v>
+        <v>-1.312539950414681</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.129317518095739</v>
+        <v>-1.127246520553562</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3668</v>
+        <v>3669</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.7683636122501838</v>
+        <v>-0.7698894145647728</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.6267510636090137</v>
+        <v>-0.6283694422615866</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.8439958884797036</v>
+        <v>-0.8455691605271269</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.9710413190175871</v>
+        <v>-0.9725766061348011</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.8150381157628246</v>
+        <v>-0.8166344920856758</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.9653401903957786</v>
+        <v>-0.9668867057397463</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.144320093628849</v>
+        <v>-1.1458215815504</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.24309004101999</v>
+        <v>-1.244580986516475</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.316635684387279</v>
+        <v>-1.318109478938872</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.226154418406935</v>
+        <v>-1.227681905661093</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.252523788882677</v>
+        <v>-1.254051756203836</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.421130855377243</v>
+        <v>-1.422612614132852</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.472123299987075</v>
+        <v>-1.473605986728032</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.234617848177052</v>
+        <v>-1.23283160340894</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3745</v>
+        <v>3746</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.6307453984430822</v>
+        <v>-0.6320200475601538</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3919429951917976</v>
+        <v>-0.3933261789467721</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6926388932319512</v>
+        <v>-0.693953625467941</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7877366949129865</v>
+        <v>-0.7890232316445136</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.5926518122727842</v>
+        <v>-0.5940058273146107</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.7070629529184487</v>
+        <v>-0.7083790187529075</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.8573874101076768</v>
+        <v>-0.8586664670493178</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9636436019865613</v>
+        <v>-0.9649079232613147</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.036857120089238</v>
+        <v>-1.038104306665446</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.9389463844272044</v>
+        <v>-0.9402438441310039</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.9955847934333306</v>
+        <v>-0.9968735166616725</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.159951884952953</v>
+        <v>-1.161196519192764</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.138379462461174</v>
+        <v>-1.139642176260949</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.060747343993363</v>
+        <v>-1.059258614788533</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3814</v>
+        <v>3815</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.4683533972938534</v>
+        <v>-0.4694217776607914</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2106052421130755</v>
+        <v>-0.2117781100105134</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.5652401168949979</v>
+        <v>-0.5663298596339317</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.6823890134394688</v>
+        <v>-0.6834457503857649</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.4743579035067498</v>
+        <v>-0.4754818509149459</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5813027552158019</v>
+        <v>-0.5823925568103405</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.7042386959821201</v>
+        <v>-0.7052988419448027</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7907961518825104</v>
+        <v>-0.7918448541153325</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.8637437396231533</v>
+        <v>-0.8647753095812476</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.7305373950420844</v>
+        <v>-0.7316237865243025</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.8159972659730457</v>
+        <v>-0.8170665319878481</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.7932853861354445</v>
+        <v>-0.7943604051839017</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.8582449161491184</v>
+        <v>-0.8593130911899536</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.8036452333658701</v>
+        <v>-0.8024394581030876</v>
       </c>
     </row>
     <row r="29">
@@ -5107,46 +5107,46 @@
         <v>3864</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.2623317945458012</v>
+        <v>-0.2498095048701785</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.08024413131664687</v>
+        <v>-0.06733432174059573</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3321387042869546</v>
+        <v>-0.3191315728693525</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5234736610094757</v>
+        <v>-0.5104945186110115</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2992183581766241</v>
+        <v>-0.2861075538016848</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2975902555942156</v>
+        <v>-0.3103738055808307</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.4716256994154691</v>
+        <v>-0.4843925631723422</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.5888804897208999</v>
+        <v>-0.6015392737073171</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6616214864199037</v>
+        <v>-0.6742692194217241</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.6186334598913916</v>
+        <v>-0.6310814863233603</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.6280273284262208</v>
+        <v>-0.6404298743849992</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.5533828221496719</v>
+        <v>-0.5657970621414137</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.6228765957552156</v>
+        <v>-0.635193770619658</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.5398112165964406</v>
+        <v>-0.5502408522945927</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3921</v>
+        <v>3922</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1294322195490665</v>
+        <v>-0.1302171741175755</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.07754591071083894</v>
+        <v>0.07668282810491434</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2018134983669597</v>
+        <v>-0.2026121302703316</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.3375745944184771</v>
+        <v>-0.3383370728014867</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.2261148799963095</v>
+        <v>-0.226914514146479</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2201766496254578</v>
+        <v>-0.2209735574366647</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2146887706312057</v>
+        <v>-0.2154888059034406</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.4133515043423941</v>
+        <v>-0.4141086753924341</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.5113485447793451</v>
+        <v>-0.5120821142640963</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.4812922838857503</v>
+        <v>-0.4820472063317283</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.468004742584597</v>
+        <v>-0.4687666584421564</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.4193951265204561</v>
+        <v>-0.420169296519056</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.4684552897314873</v>
+        <v>-0.4692239485697769</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.3319204357872678</v>
+        <v>-0.3311523743874147</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3968</v>
+        <v>3969</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.09454357014718084</v>
+        <v>-0.09518021938416865</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.3170986195895793</v>
+        <v>0.3163379668313624</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.08669890282781978</v>
+        <v>0.08599081325481706</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.07098497322667185</v>
+        <v>-0.07165213455626684</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.05800609295183534</v>
+        <v>0.05729938731793283</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.0171598150777541</v>
+        <v>0.01646678816376834</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.04679786298775923</v>
+        <v>0.04609597383633712</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.1046477053043589</v>
+        <v>-0.1053177340456699</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.2272992712764292</v>
+        <v>-0.2279395420135231</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2579390019953181</v>
+        <v>-0.2585826309419872</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.2219933311052031</v>
+        <v>-0.2226489298836398</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.1483012546250109</v>
+        <v>-0.1489753113806245</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.2016887156872897</v>
+        <v>-0.202354982946261</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.03854435290847391</v>
+        <v>-0.03798280898065087</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4013</v>
+        <v>4014</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.01525517209007887</v>
+        <v>0.01473830271621068</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.2552365140307415</v>
+        <v>0.2546440264266607</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.1223857618196362</v>
+        <v>0.1218221438206939</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.03206847161771265</v>
+        <v>-0.03259269876087956</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.08946495255317188</v>
+        <v>0.08890498544543846</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.05241236494547508</v>
+        <v>0.05186425697593222</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1056545230835084</v>
+        <v>0.1050920792927457</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.0004519640693416704</v>
+        <v>-8.915993508651354e-05</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.09659496644730581</v>
+        <v>-0.09711280594994065</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.06169975595112476</v>
+        <v>-0.06223488444957326</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.0782030929141655</v>
+        <v>-0.07873638899811652</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.004915776364960323</v>
+        <v>-0.00546724844225821</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.01235803903851718</v>
+        <v>0.01179786327587351</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.1266885494331049</v>
+        <v>0.1270857097073375</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4041</v>
+        <v>4042</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.0514057597758395</v>
+        <v>-0.05181615383891369</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.175767736206474</v>
+        <v>0.1752881082715803</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.09044512528347326</v>
+        <v>0.08998314104228911</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.03736386855557328</v>
+        <v>-0.03779347828904633</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1289883148015463</v>
+        <v>0.1285130818925921</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.094258614344092</v>
+        <v>0.09379413646589541</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.1218531740972182</v>
+        <v>0.1213809760203475</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.01415017899149973</v>
+        <v>0.01370058698249466</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.08264390539159905</v>
+        <v>-0.08307029119131215</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.05387146869360038</v>
+        <v>-0.05431205965250285</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.09640427434078447</v>
+        <v>-0.09683622612420351</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.04812500073966675</v>
+        <v>-0.04856882827524345</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.01558770502450102</v>
+        <v>0.01512449303952934</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1061107847530778</v>
+        <v>0.1064380359420696</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4061</v>
+        <v>4062</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.06339413758846746</v>
+        <v>-0.06373811642392724</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1547474579379724</v>
+        <v>0.1543387207808067</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.09245727771444479</v>
+        <v>0.09206093800082016</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.009519425610875487</v>
+        <v>-0.009890015059554003</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1533763391895704</v>
+        <v>0.1529618610635382</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1448613894786916</v>
+        <v>0.1444508537892801</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1719161353760299</v>
+        <v>0.1714981781657769</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.08704580682742602</v>
+        <v>0.08664530931159931</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.009554283558664167</v>
+        <v>-0.009931637424948292</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.01491191382501</v>
+        <v>0.01452251100917579</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.02840229610141876</v>
+        <v>-0.02878264076758086</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.04443766656027748</v>
+        <v>0.04403944917672931</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.08117184360290253</v>
+        <v>0.08076149921040354</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1478706310856239</v>
+        <v>0.1481346381623325</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4080</v>
+        <v>4081</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.03802664173452541</v>
+        <v>-0.03831710527787635</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1471874803155018</v>
+        <v>0.1468424158594317</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.0589069427273472</v>
+        <v>0.05858103710131957</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.01754926755452146</v>
+        <v>-0.01785589348644123</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1665416421567798</v>
+        <v>0.1661867765159784</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2083756029557051</v>
+        <v>0.2080120472110707</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.2349261974983179</v>
+        <v>0.2345554981052373</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.1238197117611861</v>
+        <v>0.123473355357298</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1008336183848471</v>
+        <v>0.1004923775537279</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1212579821828541</v>
+        <v>0.1209067066645773</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.05272677565953643</v>
+        <v>0.05239094276060996</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1254076128363693</v>
+        <v>0.1250540169736709</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1600340180031097</v>
+        <v>0.1596693618148493</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.203094641398927</v>
+        <v>0.203295329871608</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/roc/roc_14.xlsx
+++ b/workspaces/btc_daily_14days/roc/roc_14.xlsx
@@ -575,46 +575,46 @@
         <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.36028416735796</v>
+        <v>1.331198580560581</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-7.914904876503464</v>
+        <v>-7.916150883829857</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>7.032206623970168</v>
+        <v>7.032106763595287</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>18.6736973891183</v>
+        <v>18.67333124227142</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.790784801128268</v>
+        <v>2.83923975944127</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.7500987906748477</v>
+        <v>-0.7261926409148387</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>10.68388056887207</v>
+        <v>10.73185766362325</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-8.982096046307795</v>
+        <v>-8.932959279518862</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.362277008272919</v>
+        <v>-1.289117716696516</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.473034750972317</v>
+        <v>5.572295531932546</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.269801475051182</v>
+        <v>5.369643639333212</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>9.149633686598143</v>
+        <v>9.273279713051771</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>4.886596255948248</v>
+        <v>5.03525131812863</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>8.959633331492633</v>
+        <v>9.131632091061043</v>
       </c>
     </row>
     <row r="7">
@@ -627,1450 +627,1450 @@
         <v>40</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.986119660628987</v>
+        <v>9.957112160233216</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>15.86057286485647</v>
+        <v>15.85951841983283</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>12.9771390010881</v>
+        <v>12.97708526404308</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.628499809698482</v>
+        <v>5.628049294745352</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>17.56525050866519</v>
+        <v>17.61379455970812</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.391531547451734</v>
+        <v>5.415470168920407</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2.812684853622009</v>
+        <v>2.860624780279963</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9.836156164068363</v>
+        <v>9.88536723777225</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7.280836754026808</v>
+        <v>7.354023731117088</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>8.931042924355125</v>
+        <v>9.030311923986446</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>16.22309458830271</v>
+        <v>16.32295818502442</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>16.26140312916834</v>
+        <v>16.38505819922968</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>23.34351886124001</v>
+        <v>23.49218596671994</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>21.07501794687838</v>
+        <v>21.24701670644505</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.1884</t>
+          <t>X ≈ -0.1885</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>57</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-6.845370306823241</v>
+        <v>-6.874523703725679</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.205588520926327</v>
+        <v>-3.206796260306731</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-5.350001490508532</v>
+        <v>-5.350191134856864</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.221643953315123</v>
+        <v>-5.222168174123858</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-5.759879702370874</v>
+        <v>-5.71147966132213</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-5.463987254187202</v>
+        <v>-5.440109039652299</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-5.549841953883245</v>
+        <v>-5.501944353154819</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.7621681217088394</v>
+        <v>-0.7130014148548867</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.681167593247046</v>
+        <v>2.754337374354698</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3.585354607019575</v>
+        <v>3.684607327962929</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.877514105689031</v>
+        <v>-1.777688777078552</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.09018023954200061</v>
+        <v>0.03345147274495019</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>2.997640866024732</v>
+        <v>3.146293571485373</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.46975478898171</v>
+        <v>1.641753548548373</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.1672</t>
+          <t>X ≈ -0.1673</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>75</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3.506667978168721</v>
+        <v>3.477611532730464</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>9.877104668032437</v>
+        <v>9.876009188336575</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.14477601272382</v>
+        <v>12.14472340244254</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>5.628022218498764</v>
+        <v>5.627574552701496</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2284243643255834</v>
+        <v>-0.1799942972894328</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5.391207281987342</v>
+        <v>5.415144832565794</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2.646236251940984</v>
+        <v>2.694170733180492</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3.511970374933064</v>
+        <v>3.5611528568921</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2.120375911380286</v>
+        <v>2.193541009880818</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>2.603789799208265</v>
+        <v>2.703036801212143</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>5.064540729333267</v>
+        <v>5.164378255035018</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>6.432777013307593</v>
+        <v>6.556416008948595</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>6.014381836068218</v>
+        <v>6.163035560423772</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>10.24168461354451</v>
+        <v>9.080350039776626</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.146</t>
+          <t>X ≈ -0.1461</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.9325722118149</v>
+        <v>-1.942601385004458</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>4.373812448150822</v>
+        <v>4.319177024256362</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.111732318731818</v>
+        <v>5.047630815906771</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4.110773445472738</v>
+        <v>4.058007159985273</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>10.37122139840336</v>
+        <v>10.29708524066699</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.867348463631657</v>
+        <v>3.84492766936566</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.7562238034534445</v>
+        <v>-0.7005443225546841</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>5.580439829215138</v>
+        <v>5.565249745317914</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.790060450006713</v>
+        <v>7.774105368026568</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1208110230070858</v>
+        <v>0.2186393237405113</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.357495314682161</v>
+        <v>-2.230709128794359</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.185832027903828</v>
+        <v>-1.05021835197379</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-1.610517815698863</v>
+        <v>-1.445520799436693</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-3.015891144032359</v>
+        <v>-3.44399452951064</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.1248</t>
+          <t>X ≈ -0.1249</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.1724284172896162</v>
+        <v>-0.2025217842275069</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.21127129490511</v>
+        <v>5.119502552088136</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.476718301563771</v>
+        <v>2.427042126617877</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7.287591094909175</v>
+        <v>7.160356485907528</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>8.303839266586778</v>
+        <v>8.209088956233913</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>10.16416600446627</v>
+        <v>10.01940247211252</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>8.51746999087726</v>
+        <v>8.426477257427102</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>8.04707655695114</v>
+        <v>7.96357474928935</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.302371923278798</v>
+        <v>3.319749515607832</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.0951068437275211</v>
+        <v>0.1927241351259852</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.448998571482804</v>
+        <v>1.526051452933224</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.362310520880861</v>
+        <v>0.04687910016443908</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.181967703348576</v>
+        <v>-1.886176531866866</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-3.299982053122754</v>
+        <v>-3.945290985863778</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.1036</t>
+          <t>X ≈ -0.1037</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>137</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-6.859970128177352</v>
+        <v>-5.810690528703866</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-12.84904243899294</v>
+        <v>-12.50502167567052</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-12.52032035724885</v>
+        <v>-11.44940822755136</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-13.12068940056547</v>
+        <v>-12.04767825274662</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.376477851679446</v>
+        <v>-5.260892167461932</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-12.64216200691355</v>
+        <v>-11.87944189159784</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-14.19109033441062</v>
+        <v>-13.40240979913094</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-18.31230849226274</v>
+        <v>-17.84430421621712</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-14.73138599256595</v>
+        <v>-14.2414148885258</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-14.86354562954703</v>
+        <v>-14.33887045740979</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-15.38903259363191</v>
+        <v>-15.27618860893855</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-18.27436247047367</v>
+        <v>-18.14048882345323</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-17.9645863164883</v>
+        <v>-17.81089346639497</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-15.54906964436363</v>
+        <v>-15.3770708847968</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.08244</t>
+          <t>X ≈ -0.08252</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.932315186033691</v>
+        <v>-4.570083658533946</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-10.20839442447305</v>
+        <v>-10.26602200149814</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-11.1891851403291</v>
+        <v>-10.6636079157504</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-12.81390052386956</v>
+        <v>-12.2969431291976</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-8.684129810327242</v>
+        <v>-9.267343800032911</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-7.804828514320825</v>
+        <v>-8.408292848424786</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-9.644267385843207</v>
+        <v>-10.49767482924046</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-8.360585309472789</v>
+        <v>-9.200936334057701</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-10.76258777296103</v>
+        <v>-11.5900522417618</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-9.861413434774285</v>
+        <v>-10.65349371300378</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-11.23570523630946</v>
+        <v>-11.44844903366436</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.938169189217298</v>
+        <v>-6.102913750274034</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-9.867091972355141</v>
+        <v>-10.02829130571436</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-10.22615164376603</v>
+        <v>-10.37063035237976</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.06124</t>
+          <t>X ≈ -0.06134</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.1452518618396255</v>
+        <v>-0.2237382874285672</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-3.166307869518256</v>
+        <v>-3.703360143975232</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.437444238214702</v>
+        <v>-5.969590980019845</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.496114263017112</v>
+        <v>-2.570894690497965</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-6.786444352868159</v>
+        <v>-6.540326367644838</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-1.33237024611617</v>
+        <v>-0.2012556844508779</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.827251549216413</v>
+        <v>-1.669026631035862</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>1.865091141558274</v>
+        <v>2.99386511131388</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.742391249985452</v>
+        <v>3.682650063330009</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.1916992431921472</v>
+        <v>0.315276572465983</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.3964004014522402</v>
+        <v>-0.5559120333904772</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.648407225622726</v>
+        <v>-3.767464394652897</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-4.538041647011262</v>
+        <v>-4.631048555578495</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-5.720756701010082</v>
+        <v>-5.785693573929926</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.04004</t>
+          <t>X ≈ -0.04016</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.2610647696319575</v>
+        <v>-0.2753484336452132</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1752728129752938</v>
+        <v>0.8891477669144692</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.2186958306351201</v>
+        <v>0.1528770923483194</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.792932587654782</v>
+        <v>-1.434248115782559</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.076552048370829</v>
+        <v>1.509597016783793</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.01029187849085389</v>
+        <v>0.06576908556774441</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.097250381952016</v>
+        <v>-0.680789674982293</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.906137322094779</v>
+        <v>-1.489706397579461</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2.991895013671453</v>
+        <v>-2.556361929650961</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.7701414550524319</v>
+        <v>-0.9758507740207634</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.414235884980819</v>
+        <v>1.223353815750627</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.5991675326297425</v>
+        <v>-0.7790185219716861</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-1.701912242598517</v>
+        <v>-1.861678318819216</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.452285807388968</v>
+        <v>0.1044050225951878</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.01884</t>
+          <t>X ≈ -0.01897</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-4.29592992890246</v>
+        <v>-3.764626351453856</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.302188542410896</v>
+        <v>-2.467251471567486</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.4753325157155217</v>
+        <v>-0.790738671232134</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.735723167941892</v>
+        <v>-2.156035097690328</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-3.666395255012112</v>
+        <v>-4.017347251713531</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-3.927159386893386</v>
+        <v>-4.018999437548615</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-3.30389215707374</v>
+        <v>-3.529943382806358</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-5.444681691535273</v>
+        <v>-5.641858493585111</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-5.07104928178444</v>
+        <v>-5.404100540937023</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-5.085313482014023</v>
+        <v>-4.854527333225171</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-5.011463108240783</v>
+        <v>-4.784104565908173</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-6.091291084019232</v>
+        <v>-5.826349600636583</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.1688235529314</v>
+        <v>-2.928690166744694</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.614397094905492</v>
+        <v>-4.879356919929776</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 0.002368</t>
+          <t>X ≈ 0.00221</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-2.492289808522344</v>
+        <v>-2.253595599744997</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-4.631941521259868</v>
+        <v>-4.102011689656017</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-6.591577907920801</v>
+        <v>-6.069469754056641</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-9.178773891090785</v>
+        <v>-8.561647326661927</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-7.379581771364215</v>
+        <v>-6.953341114184518</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-7.346499258966986</v>
+        <v>-7.20499475745148</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-6.391734835334013</v>
+        <v>-6.218114488599376</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-6.451426224611701</v>
+        <v>-6.422599945901119</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-4.168658381134485</v>
+        <v>-4.10006601378457</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.456077177464344</v>
+        <v>-3.614742540221698</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.619111669057865</v>
+        <v>-2.507986377457236</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.5014001833691495</v>
+        <v>-0.4610581334031494</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.4007177033492866</v>
+        <v>-0.3326937867374937</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.216648719789418</v>
+        <v>-1.134873057335682</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.02357</t>
+          <t>X ≈ 0.02339</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.7795032130017674</v>
+        <v>0.3487244884588989</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.741821039413523</v>
+        <v>-2.292933284240171</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.8954196362507147</v>
+        <v>0.1899463309223606</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.336956821501893</v>
+        <v>1.364975092081679</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2242801047941398</v>
+        <v>-0.4319397606157622</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.570415114399204</v>
+        <v>1.149252357037554</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2.798040713138285</v>
+        <v>2.131765288853181</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.543570494548398</v>
+        <v>1.139408770690565</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>4.369727445637203</v>
+        <v>4.244291342824148</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.519808649307308</v>
+        <v>3.676315770010696</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.527705916243967</v>
+        <v>2.687328933064329</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.349485643402417</v>
+        <v>3.269549804579277</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.454269173291131</v>
+        <v>3.289709031533974</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.680004823517663</v>
+        <v>3.69466068550156</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.04477</t>
+          <t>X ≈ 0.04458</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.9823937829292788</v>
+        <v>0.4310646457012552</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.672612037342518</v>
+        <v>2.115861416754548</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2923262682438903</v>
+        <v>-0.2386608852856469</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.745524389975273</v>
+        <v>1.525210084033645</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.199576494726031</v>
+        <v>2.016353099944432</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3.680581807138772</v>
+        <v>3.269530775626066</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.609116480985151</v>
+        <v>1.574887758296107</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2.79767697627134</v>
+        <v>2.743041926017263</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.08768819723192678</v>
+        <v>-0.2351071537077232</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>2.880153506862371</v>
+        <v>2.535835507307425</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.006578176416753</v>
+        <v>2.658492445392262</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.385327189699261</v>
+        <v>1.409469640273407</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.620805475458667</v>
+        <v>2.648298641814129</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.846541125685199</v>
+        <v>2.897343503829497</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.06597</t>
+          <t>X ≈ 0.06576</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.9881302369716281</v>
+        <v>-0.4501867312540213</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.7863398192166429</v>
+        <v>1.337422700444058</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.119715324324922</v>
+        <v>-0.5544426286946234</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6121316901705214</v>
+        <v>-0.4245585874799858</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-2.064749238615271</v>
+        <v>-2.03740323404984</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.012658227848107</v>
+        <v>-1.015554044818927</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.097368587114232</v>
+        <v>-1.450741969250423</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.187078740335025</v>
+        <v>-1.54204289442773</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.62541938742379</v>
+        <v>-1.95354733877052</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.9659042214894527</v>
+        <v>-1.279248578761525</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.170605379749645</v>
+        <v>-1.483389026297615</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-2.26830269909248</v>
+        <v>-2.548817794550708</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-3.820529024104005</v>
+        <v>-4.067571226732468</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-3.217434883311434</v>
+        <v>-3.443994529511109</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.08717</t>
+          <t>X ≈ 0.08694</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-1.995479137330527</v>
+        <v>-2.019915746455617</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-4.577539016802007</v>
+        <v>-4.583484988474261</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-3.996830819926174</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-6.298395937580388</v>
+        <v>-6.317927170868352</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-4.356195919663413</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-4.112126995021583</v>
+        <v>-4.083410400844535</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.740526674676104</v>
+        <v>-2.183282176344449</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.2949739592395417</v>
+        <v>0.2920615338603909</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.297703688577847</v>
+        <v>-1.705695389001903</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.603933164519411</v>
+        <v>-4.000112205110938</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.896012963556309</v>
+        <v>-1.263076182058853</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.861634811200986</v>
+        <v>-1.695105523125342</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.796348771310456</v>
+        <v>-1.60006737125773</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.085176227880041</v>
+        <v>-0.8608264308109881</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.1084</t>
+          <t>X ≈ 0.1081</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.022268682841407</v>
+        <v>0.05399073921558539</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>3.232738640733025</v>
+        <v>2.316967500213686</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.564081905659521</v>
+        <v>-0.6408730522036947</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.4204216989293741</v>
+        <v>-1.152014652014692</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.391753204484758</v>
+        <v>-2.923315075017854</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-7.463805926442028</v>
+        <v>-8.419760325429621</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-4.363802909912017</v>
+        <v>-5.916313850552598</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.556986203380283</v>
+        <v>-5.100095328884578</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-4.254911035062264</v>
+        <v>-5.778093579047017</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.920116455595981</v>
+        <v>-2.755768313708231</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.2139895883784604</v>
+        <v>-1.677857479192966</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.731216589454647</v>
+        <v>1.585437463300131</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.31106573614116</v>
+        <v>1.190279536736227</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.173744061526925</v>
+        <v>2.721375680802886</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.1296</t>
+          <t>X ≈ 0.1293</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3.6166449450755</v>
+        <v>4.289888175113013</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>11.76155641298719</v>
+        <v>11.50671108995711</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>15.43182567863865</v>
+        <v>15.91297310164245</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>13.93603456206446</v>
+        <v>14.44285714285724</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>10.1457124886435</v>
+        <v>9.953608001905216</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>8.004062128034647</v>
+        <v>8.62639352072415</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>7.919351768768522</v>
+        <v>8.56573743149869</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>5.826266864819189</v>
+        <v>5.699904671115341</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>4.952276578215063</v>
+        <v>4.862932061978547</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>9.793414692454363</v>
+        <v>8.839103481163562</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>7.149689143950262</v>
+        <v>7.034963033627427</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>5.558051036143034</v>
+        <v>4.693129770992364</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>2.698875792585675</v>
+        <v>1.89797184442854</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>6.989652093218751</v>
+        <v>5.34701670644391</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.1508</t>
+          <t>X ≈ 0.1505</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.200902151283771</v>
+        <v>2.662301968216397</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.862443330947279</v>
+        <v>4.52740074512964</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.19494467346496</v>
+        <v>1.834812182102226</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.870624362507868</v>
+        <v>5.41297208538581</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>6.468698445775814</v>
+        <v>7.2225735191466</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>9.038799748138238</v>
+        <v>7.495359037965528</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.954089388871999</v>
+        <v>7.434702948740068</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.941566199630721</v>
+        <v>4.670019613644087</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.471493134017031</v>
+        <v>2.334196429794638</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.167028883141718</v>
+        <v>4.958643711048623</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.719490456936661</v>
+        <v>-0.9926231732690098</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.821475940945035</v>
+        <v>-2.083881723260504</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.9688995215311067</v>
+        <v>-0.1801890751117554</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.393199765059002</v>
+        <v>1.218281074259998</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.172</t>
+          <t>X ≈ 0.1717</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-3.567872552273485</v>
+        <v>-3.036427614360612</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.342680485097475</v>
+        <v>1.696184774167627</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.034865622081561</v>
+        <v>2.355078364800349</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.00882227780827094</v>
+        <v>1.43233082706773</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.800714256052494</v>
+        <v>4.100976422957842</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.8372187204701191</v>
+        <v>2.268498783881988</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2.92642140468228</v>
+        <v>4.31310585255131</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.546309282634731</v>
+        <v>3.847273092168038</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.572283647851023</v>
+        <v>3.81030048303117</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.799374278913611</v>
+        <v>-2.276685992520648</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-5.638721176898841</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-9.491436415253268</v>
+        <v>-8.738449176376058</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-7.737674225088419</v>
+        <v>-7.028343945045087</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-5.338025531383622</v>
+        <v>-4.674035925135037</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.1932</t>
+          <t>X ≈ 0.1929</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>5.960642411024089</v>
+        <v>6.700414490902453</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>10.84296281146675</v>
+        <v>11.69618477416766</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.552087530607892</v>
+        <v>7.355078364800278</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7.981013972897337</v>
+        <v>8.800751879699177</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>10.04012701720438</v>
+        <v>9.627292212431463</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>11.63620234554085</v>
+        <v>11.21586720493474</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>12.8501932849759</v>
+        <v>12.4710005893935</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>12.38312464118902</v>
+        <v>12.00516782901</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>12.3221424846663</v>
+        <v>11.96819521987329</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>12.77092498703774</v>
+        <v>12.46015611274251</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>11.26752253007641</v>
+        <v>10.94022619152229</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>11.30190068243157</v>
+        <v>10.99839292888702</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>14.77785372522214</v>
+        <v>14.55060342337598</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.211381583240879</v>
+        <v>6.904911443286011</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.2144</t>
+          <t>X ≈ 0.214</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>69</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>8.388649186856959</v>
+        <v>6.91017803018552</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>9.676013818430796</v>
+        <v>8.225551669667354</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.382691709037999</v>
+        <v>4.933262956715012</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.063641490307695</v>
+        <v>3.613871635610764</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>5.974627299530759</v>
+        <v>6.023173219296602</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>6.272001329165796</v>
+        <v>6.295958738115459</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>7.636566332218507</v>
+        <v>9.133853373527586</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>8.618773050750654</v>
+        <v>10.11729597546317</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>8.557790894227963</v>
+        <v>10.08032336632638</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>10.60642282253578</v>
+        <v>12.15504551014908</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.952446301956542</v>
+        <v>10.5016297002941</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>19.13175199054391</v>
+        <v>20.704723973891</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>14.36377505027386</v>
+        <v>15.96173996037049</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>13.14023533818159</v>
+        <v>14.7615094600671</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.2356</t>
+          <t>X ≈ 0.2352</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>16.90683907150646</v>
+        <v>17.48988817511302</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>11.21402032538141</v>
+        <v>11.90671108995716</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>18.98251424674883</v>
+        <v>19.51297310164246</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>12.99029041074534</v>
+        <v>13.64285714285714</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>14.49281718418026</v>
+        <v>15.15360800190522</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>20.91264019340724</v>
+        <v>21.42639352072415</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>16.7462971810798</v>
+        <v>15.36573743149869</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>14.2384122107625</v>
+        <v>12.89990467111534</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>14.17743005423966</v>
+        <v>12.8629320619786</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>7.205062278317911</v>
+        <v>6.039103481163565</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>13.12281009964961</v>
+        <v>11.83496303362742</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>17.23882090506617</v>
+        <v>15.89312977099237</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>16.81867005175276</v>
+        <v>15.49797184442848</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>19.0852220285099</v>
+        <v>17.74701670644391</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.2568</t>
+          <t>X ≈ 0.2564</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7.863911555672601</v>
+        <v>8.893396947042845</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>9.701001324677733</v>
+        <v>10.81899179171155</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.582092008888161</v>
+        <v>8.670867838484519</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>11.16059301454549</v>
+        <v>12.30952380952385</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>3.725751737311811</v>
+        <v>3.048344844010529</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.747263697981381</v>
+        <v>6.829902292653976</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>17.73151885595664</v>
+        <v>19.04994795781452</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>12.09203641906645</v>
+        <v>11.56657133778196</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>10.30691633150914</v>
+        <v>9.775212763732931</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>9.456997535179383</v>
+        <v>8.951384182917991</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.97643430795367</v>
+        <v>12.25601566520646</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>9.286674529274471</v>
+        <v>10.55979643765908</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10.59066160699564</v>
+        <v>11.91902447600759</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>14.26467311929104</v>
+        <v>15.67684126784741</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.278</t>
+          <t>X ≈ 0.2776</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.838232905635799</v>
+        <v>1.65655484177968</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>20.37598298278473</v>
+        <v>18.82337775662382</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>24.23653074696593</v>
+        <v>22.59630643497586</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>22.23909631608621</v>
+        <v>20.64285714285708</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>23.82846633745866</v>
+        <v>24.32027466857182</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>19.87052121815758</v>
+        <v>18.3430601873908</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>21.91347043335944</v>
+        <v>20.36573743149863</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>25.70172093850883</v>
+        <v>26.14990467111537</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>23.513079207518</v>
+        <v>24.02959872864515</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>18.40784126225188</v>
+        <v>19.03910348116348</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>20.33079967845981</v>
+        <v>18.83496303362742</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>22.49283740528328</v>
+        <v>20.97646310432564</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>22.0726865519698</v>
+        <v>20.58130517776181</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>24.42608177666445</v>
+        <v>22.91368337311055</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.2992</t>
+          <t>X ≈ 0.2988</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>9.741306191687869</v>
+        <v>8.853524538749411</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-5.203213234709324</v>
+        <v>-6.36601618277011</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.290904269424551</v>
+        <v>2.33115491982425</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.421129413012913</v>
+        <v>2.461038961038959</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2.882839859917219</v>
+        <v>1.971789820087011</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>3.180213889552306</v>
+        <v>2.244575338905967</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>5.317725752508366</v>
+        <v>4.45664652240778</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>9.295101553166099</v>
+        <v>8.536268307479013</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>11.45634161886551</v>
+        <v>10.77202297106945</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>17.27308948920235</v>
+        <v>16.76637620843633</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>12.62394388649773</v>
+        <v>12.01678121544565</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>12.65832203885301</v>
+        <v>12.07494795281054</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>18.90483785220627</v>
+        <v>18.49797184442854</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>14.68612905798839</v>
+        <v>14.2015621609894</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.3204</t>
+          <t>X ≈ 0.32</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>28</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-9.623773173391498</v>
+        <v>-6.081540396315603</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-11.23495926645533</v>
+        <v>-7.664717481471406</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-4.48687350835327</v>
+        <v>-0.9155983269288726</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.7852197933362319</v>
+        <v>2.785714285714235</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.819347796425113</v>
+        <v>9.439322287619611</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>6.1167218260602</v>
+        <v>9.712107806438439</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.460582895365462</v>
+        <v>6.080023145784395</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.993514251578823</v>
+        <v>5.61419038540101</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.932532095056047</v>
+        <v>5.577217776264256</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.082613298726187</v>
+        <v>4.753389195449273</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.693516430962731</v>
+        <v>0.9778201764846131</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-6.230566850035821</v>
+        <v>-2.535441657579064</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.4921394395078522</v>
+        <v>4.212257558714249</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.853553481694128</v>
+        <v>0.8898738493010043</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.3416</t>
+          <t>X ≈ 0.3412</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.480916030534317</v>
+        <v>-4.891064205839328</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.092102123598117</v>
+        <v>-6.474241290995224</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.513126491646851</v>
+        <v>-2.106074517405226</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.643351635235106</v>
+        <v>2.785714285714377</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>5.105062082139526</v>
+        <v>2.296465144762294</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>10.40243611177461</v>
+        <v>7.331155425486052</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>10.31772575250844</v>
+        <v>7.270499336260592</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>14.85065710872156</v>
+        <v>11.56657133778207</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>14.78967495219878</v>
+        <v>11.5295987286452</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>13.93975615586892</v>
+        <v>10.70577014783022</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>13.7350549976088</v>
+        <v>10.50162970029407</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>18.76943314996405</v>
+        <v>15.3217011995638</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>13.34928229665076</v>
+        <v>10.16463851109524</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>8.575017946877217</v>
+        <v>5.651778611205913</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.3628</t>
+          <t>X ≈ 0.3623</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>19</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>5.413820811570865</v>
+        <v>5.384625017218234</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-1.460523176229799</v>
+        <v>-1.461709962674455</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-7.118452455721645</v>
+        <v>-7.118605845725966</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-1.725069417396476</v>
+        <v>-1.725563909774479</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>2.999798924244715</v>
+        <v>3.048344844010487</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>13.82348874335348</v>
+        <v>13.84744615230309</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>13.73877838408731</v>
+        <v>13.78679006307763</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>8.00855184556373</v>
+        <v>8.057799407957447</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>23.73704337325148</v>
+        <v>23.81030048303118</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>22.88712457692162</v>
+        <v>22.98647190221619</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>17.41926552392469</v>
+        <v>17.51917355994337</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>17.4536436762799</v>
+        <v>17.57734029730815</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>17.03349282296647</v>
+        <v>17.18218237074429</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>11.99607057845612</v>
+        <v>12.16806933802278</v>
       </c>
     </row>
   </sheetData>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4081</v>
+        <v>4092</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.1848730407932635</v>
+        <v>-0.1836806434009972</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.02418128313886569</v>
+        <v>-0.02408813031573942</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.11248445654482</v>
+        <v>-0.1121792259227377</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.2134071034595522</v>
+        <v>-0.2128230131643107</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.1761115119925805</v>
+        <v>-0.1767992158465503</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.08545823892245608</v>
+        <v>-0.08580160122706815</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.01006289719808962</v>
+        <v>-0.01118376879406924</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.07453770573655305</v>
+        <v>0.07315991757702989</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1739138166139327</v>
+        <v>0.1716945711315887</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.2188259233108525</v>
+        <v>0.2158612936635649</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2482773286567976</v>
+        <v>0.2452194438838831</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1985294027194513</v>
+        <v>0.195034998154064</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.233162747410141</v>
+        <v>0.2289759978612267</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.203295329871608</v>
+        <v>0.1986296096697231</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4055</v>
+        <v>4066</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1947803373190098</v>
+        <v>-0.1933675248134392</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.02641275223166417</v>
+        <v>0.02637759314499988</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1582950528687093</v>
+        <v>-0.1578632976707581</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.3345081433626405</v>
+        <v>-0.333590354689477</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.1951347682542561</v>
+        <v>-0.1960852496285241</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.08119667188285717</v>
+        <v>-0.08170662655125938</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-0.07863072213466182</v>
+        <v>-0.07988004947356586</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1326073672786379</v>
+        <v>0.1307494648285044</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1837636221495842</v>
+        <v>0.1810357220129362</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.1851367914935338</v>
+        <v>0.1816096236697078</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2160801331435422</v>
+        <v>0.2124513599975941</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1411363789510602</v>
+        <v>0.1369842449353342</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.2033256891556405</v>
+        <v>0.1982423140621776</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1471511158044976</v>
+        <v>0.1415076065914747</v>
       </c>
     </row>
     <row r="8">
@@ -2318,1453 +2318,1453 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4015</v>
+        <v>4026</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.296208979888867</v>
+        <v>-0.2942168013663107</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.131337286250286</v>
+        <v>-0.1309313072691864</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.2891586549006604</v>
+        <v>-0.2883645253082534</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.3939154455101956</v>
+        <v>-0.3928217471329418</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.372075094798916</v>
+        <v>-0.3730338816139849</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.1357194934951664</v>
+        <v>-0.1363233855723394</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-0.1074358586303745</v>
+        <v>-0.1090951992972506</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.03593440292705452</v>
+        <v>0.0338332425439134</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1130580367759677</v>
+        <v>0.1097690751266427</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.09800447634672338</v>
+        <v>0.09369405188316193</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.05660800905727825</v>
+        <v>0.05238671195956357</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.01946403699132304</v>
+        <v>-0.02444719027872821</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.02721172725366472</v>
+        <v>-0.03319279426030874</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.06134568948639441</v>
+        <v>-0.0681844858064693</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.1778</t>
+          <t>X &gt; -0.1779</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3958</v>
+        <v>3969</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2018931143923268</v>
+        <v>-0.1997150393520783</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.08706434022285947</v>
+        <v>-0.0867578876866375</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.2162763806132375</v>
+        <v>-0.2156701144379412</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.3243903002487301</v>
+        <v>-0.3234660539259693</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.2944841744776454</v>
+        <v>-0.2963668598343503</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-0.05898597597130362</v>
+        <v>-0.06015412825750133</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.02905861066943771</v>
+        <v>-0.03164687433632452</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.04742804716764226</v>
+        <v>0.04455875916566043</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.07607414472975904</v>
+        <v>0.07178963621105083</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.04778240523799582</v>
+        <v>0.04212386877997432</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.08446171308469275</v>
+        <v>0.07866897521861205</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.01844563791466669</v>
+        <v>-0.02527869035237984</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.07077327293756497</v>
+        <v>-0.07885435204500624</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.08339539319349853</v>
+        <v>-0.0927414190285063</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.1566</t>
+          <t>X &gt; -0.1567</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3883</v>
+        <v>3894</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.2735238334090937</v>
+        <v>-0.2705418223274734</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2795218925327134</v>
+        <v>-0.2786447728180477</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.455029646000888</v>
+        <v>-0.4537362453485798</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.4393609257717941</v>
+        <v>-0.438085480093676</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.2957601172439013</v>
+        <v>-0.2986082420097134</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1642562552262348</v>
+        <v>-0.1656105797371552</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.0807318310391949</v>
+        <v>-0.08414721346414922</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.01948945851930262</v>
+        <v>-0.0231722519615758</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.03658853244576221</v>
+        <v>0.03092385474592874</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.001586782129457731</v>
+        <v>-0.00912638030384727</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.01172832714673433</v>
+        <v>-0.01928382292884834</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1430507625197919</v>
+        <v>-0.15204476699531</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.1883078166345626</v>
+        <v>-0.199075652362211</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2828239279618003</v>
+        <v>-0.2694188354153582</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.1354</t>
+          <t>X &gt; -0.1355</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3795</v>
+        <v>3805</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.2350531463735948</v>
+        <v>-0.2314318877471209</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3874252975340653</v>
+        <v>-0.3861890934329324</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.5841139814149798</v>
+        <v>-0.5824147390284082</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5448712880035558</v>
+        <v>-0.5432503276540004</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.5431104132589155</v>
+        <v>-0.5464444364796748</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.2577427414606106</v>
+        <v>-0.2594181761024998</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.06506824907016551</v>
+        <v>-0.06972951498609348</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1493428912783656</v>
+        <v>-0.1538869846180546</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.143202120715074</v>
+        <v>-0.1501912976015092</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.004424992103622571</v>
+        <v>-0.01445388297400996</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.04266626966568765</v>
+        <v>0.03244202522411399</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1188703273804492</v>
+        <v>-0.1310362389892461</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1553290340475684</v>
+        <v>-0.1699209564122413</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.2194484562848089</v>
+        <v>-0.1951646338977469</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.1142</t>
+          <t>X &gt; -0.1143</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3667</v>
+        <v>3675</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.2372391200094697</v>
+        <v>-0.2324545580757018</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.5828529397026472</v>
+        <v>-0.5809482536826565</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.6909551410062775</v>
+        <v>-0.688871716588686</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.8182705748900645</v>
+        <v>-0.8157588679976726</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.8519213101829024</v>
+        <v>-0.8561639850654643</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.6215290298376672</v>
+        <v>-0.6230227160393582</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.3646496220489723</v>
+        <v>-0.3702756048945801</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.4354464335127091</v>
+        <v>-0.4410352908515094</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.2634730445305067</v>
+        <v>-0.2729375032388432</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.007899242168086573</v>
+        <v>-0.02178262919251495</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.006423049841430384</v>
+        <v>-0.02039313820504418</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1356663864416561</v>
+        <v>-0.1373298428232417</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1194932692069415</v>
+        <v>-0.109209874831528</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1119196042544672</v>
+        <v>-0.06250710307990204</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.09304</t>
+          <t>X &gt; -0.09312</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3530</v>
+        <v>3538</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.01979038370696173</v>
+        <v>-0.01645163891910073</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.1067996928463444</v>
+        <v>-0.1192190115084557</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.2318551311974346</v>
+        <v>-0.2721974650335994</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3408112606924618</v>
+        <v>-0.3808315204254313</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.6375121752862896</v>
+        <v>-0.6856021532428755</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1550058803024257</v>
+        <v>-0.1871466767370649</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.1719572837848986</v>
+        <v>0.1343604563293823</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2583581279741836</v>
+        <v>0.2328617817248286</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2980295259739805</v>
+        <v>0.2679560529466514</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.5686513400049691</v>
+        <v>0.5326099746700592</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.5905790769289041</v>
+        <v>0.5703485179539385</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.5683000054881973</v>
+        <v>0.5597964376590312</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.5730783306450462</v>
+        <v>0.5762425423658115</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.4871992499933953</v>
+        <v>0.5305102055959665</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.07184</t>
+          <t>X &gt; -0.07193</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3359</v>
+        <v>3368</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.2209842069953325</v>
+        <v>0.2133932076766598</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.4074523759563249</v>
+        <v>0.3929414719530229</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.3259607162457101</v>
+        <v>0.2523095945334575</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.2941688714907116</v>
+        <v>0.2206349206349216</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2278748976465153</v>
+        <v>-0.2524382340165374</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.2344313541176817</v>
+        <v>0.2278161644704468</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.6716817310925478</v>
+        <v>0.6710130687245339</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.6971313723336507</v>
+        <v>0.7090333018207389</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.8611035236274205</v>
+        <v>0.8664897257793243</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>1.099625164502513</v>
+        <v>1.097229222563335</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.192631657328953</v>
+        <v>1.176998038077194</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.899531393488985</v>
+        <v>0.8960971300428184</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.1045666074575</v>
+        <v>1.111507018070569</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.032594606597399</v>
+        <v>1.080745922595924</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.05064</t>
+          <t>X &gt; -0.05075</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3146</v>
+        <v>3154</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.245780228184735</v>
+        <v>0.2430527320750429</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.6494138928940529</v>
+        <v>0.6708769652341431</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7161721769259657</v>
+        <v>0.6744677184885646</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.4830850531976978</v>
+        <v>0.4100411783338629</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.2161731932505617</v>
+        <v>0.1741971688358532</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.3405116913235986</v>
+        <v>0.2569288390643507</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.9085770866888012</v>
+        <v>0.8297855784736612</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6180546301706329</v>
+        <v>0.554006666680749</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.7337308962547979</v>
+        <v>0.6754122647026506</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.187054312258063</v>
+        <v>1.150284982588964</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.300217108225453</v>
+        <v>1.294576590802009</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>1.207449678889738</v>
+        <v>1.212521405973355</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.486599524877029</v>
+        <v>1.501141416536299</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.489830407144254</v>
+        <v>1.546636237198506</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.02944</t>
+          <t>X &gt; -0.02956</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2853</v>
+        <v>2863</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2978326587351319</v>
+        <v>0.2957438739627847</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.6981076666116053</v>
+        <v>0.6486915641552145</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8121821054977829</v>
+        <v>0.727483042347032</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.7168295918481604</v>
+        <v>0.5974977569534445</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.1278132196963284</v>
+        <v>0.03846494538044709</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.3744249072927488</v>
+        <v>0.2763586288888362</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.114573388235165</v>
+        <v>0.9833229164951973</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.8772864009430705</v>
+        <v>0.7617330032856131</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.116348629030256</v>
+        <v>1.003895076633114</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.388056190919819</v>
+        <v>1.366388896376399</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>1.288507503742693</v>
+        <v>1.301815790082465</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>1.392987303486727</v>
+        <v>1.414944779718375</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.814056218837891</v>
+        <v>1.842943911467643</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.689283632120848</v>
+        <v>1.693226975392555</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.008234</t>
+          <t>X &gt; -0.00838</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2494</v>
+        <v>2499</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.9590839694656452</v>
+        <v>0.8871703493736121</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.129986711936027</v>
+        <v>1.102554415296893</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.9975140016547854</v>
+        <v>0.9486245804594091</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.069863449412161</v>
+        <v>0.9985725705150088</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.673972338549703</v>
+        <v>0.6292275063016959</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.9936184765039968</v>
+        <v>0.902013025120624</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.750591483971291</v>
+        <v>1.640717447485898</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1.787305063813854</v>
+        <v>1.694469019636529</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.006996523971104</v>
+        <v>1.937272589556486</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.319868425315661</v>
+        <v>2.272516750548057</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>2.19535972896405</v>
+        <v>2.188280379750573</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.470315267045123</v>
+        <v>2.469699143243467</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>2.531319185183186</v>
+        <v>2.537971844428547</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>2.596669911592564</v>
+        <v>2.650578131013738</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.01297</t>
+          <t>X &gt; 0.0128</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2110</v>
+        <v>2118</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.587201282616071</v>
+        <v>1.452152326056414</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.178603034944175</v>
+        <v>2.038786561655279</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.378656794677077</v>
+        <v>2.211086309189632</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2.935018301901806</v>
+        <v>2.718328840970351</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.13964284954826</v>
+        <v>1.993230643414655</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2.511440851111026</v>
+        <v>2.36035578487509</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>3.232417695636329</v>
+        <v>3.054416676781699</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>3.286676066067599</v>
+        <v>3.154621652247414</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>3.130907179687</v>
+        <v>3.023309420469111</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.371035776722074</v>
+        <v>3.331556311352244</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>3.071547888604059</v>
+        <v>3.033076241174641</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>3.011139311101566</v>
+        <v>2.996903355898027</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>3.064922107077251</v>
+        <v>3.054366370148223</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>3.290657757303784</v>
+        <v>3.331530398606333</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.03417</t>
+          <t>X &gt; 0.03399</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1729</v>
+        <v>1736</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.765184489396319</v>
+        <v>1.694957299536981</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.042502151387374</v>
+        <v>2.991964546178359</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>2.705500841733432</v>
+        <v>2.655830244499597</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.066806285726187</v>
+        <v>3.016129032258064</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>2.561709480983374</v>
+        <v>2.526879891306145</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.718803954458167</v>
+        <v>2.626854350217229</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>3.328136394497953</v>
+        <v>3.257442500623107</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>3.670784349901503</v>
+        <v>3.598061353142988</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.857922494130598</v>
+        <v>2.754637131102967</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>3.338252396470494</v>
+        <v>3.255693342914725</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>3.191388138152469</v>
+        <v>3.109156582014577</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.936581790796978</v>
+        <v>2.936908572835684</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>2.97912613702087</v>
+        <v>3.002580139359416</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>3.204861787247403</v>
+        <v>3.251625001374784</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.05537</t>
+          <t>X &gt; 0.05517</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.930848675347995</v>
+        <v>1.965412650637489</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3.120783030463443</v>
+        <v>3.179438362684436</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.216207724139771</v>
+        <v>3.275210863880226</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>3.346432867728133</v>
+        <v>3.335164835164825</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>2.638348697416248</v>
+        <v>2.636125484422699</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>2.515260218291701</v>
+        <v>2.489330583661207</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.691937385304449</v>
+        <v>3.617485683246933</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>3.855562504657151</v>
+        <v>3.781023552234224</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3.444194924168016</v>
+        <v>3.394400593447081</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.435201145357425</v>
+        <v>3.409732851792931</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>3.230499987097232</v>
+        <v>3.205592404256841</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.264878139452556</v>
+        <v>3.263759141621733</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>3.054958540518967</v>
+        <v>3.078391424848128</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>3.2806941907455</v>
+        <v>3.327436286863495</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.07657</t>
+          <t>X &gt; 0.07635</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.596536637279755</v>
+        <v>2.519982758088084</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>3.653164657813186</v>
+        <v>3.602325879295087</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>4.205036990786191</v>
+        <v>4.154417641625258</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>4.249203614581099</v>
+        <v>4.198317160054039</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3.710914061485404</v>
+        <v>3.709068019102119</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>3.319819932772816</v>
+        <v>3.293977355633864</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.78416292978892</v>
+        <v>4.781042676554577</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>5.005562444349856</v>
+        <v>5.003086098458418</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>4.600346208653235</v>
+        <v>4.622175398178037</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>4.43889557067105</v>
+        <v>4.486222999650238</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4.234194412410858</v>
+        <v>4.282082552114147</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>4.526748124146565</v>
+        <v>4.598202857836732</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>4.622948389593915</v>
+        <v>4.718952067988305</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>4.762625520026987</v>
+        <v>4.882012407217772</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.09777</t>
+          <t>X &gt; 0.09754</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>3.586029576160207</v>
+        <v>3.485717163642732</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.426726328284666</v>
+        <v>5.343624541469161</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>6.077980048132133</v>
+        <v>5.888364133967798</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6.522012723101248</v>
+        <v>6.435349322210634</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>5.565313128164554</v>
+        <v>5.424723747473521</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>4.921264563657381</v>
+        <v>4.863306972236145</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>6.40559186129498</v>
+        <v>6.262504897609219</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>6.147728238428741</v>
+        <v>6.005222710739957</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>6.086746081905964</v>
+        <v>5.968250101603161</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>6.387454900638865</v>
+        <v>6.291449675115601</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>5.555138679617166</v>
+        <v>5.46165750703728</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>5.903324363353249</v>
+        <v>5.936925391430329</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>6.006186062341087</v>
+        <v>6.063143898651688</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>6.022716691647119</v>
+        <v>6.103638187152981</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.119</t>
+          <t>X &gt; 0.1187</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>4.089797361205328</v>
+        <v>4.152403741738176</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>5.85783529817904</v>
+        <v>5.931617690206224</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>6.964941260107359</v>
+        <v>7.156808718080818</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>7.720948631480454</v>
+        <v>7.909357765522152</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>6.932346187270866</v>
+        <v>7.046509620834236</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>7.354876662462893</v>
+        <v>7.443828140898496</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>8.521730758766189</v>
+        <v>8.62850206412633</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>8.05466211497945</v>
+        <v>8.162669303742987</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>8.118836404013614</v>
+        <v>8.250229695851523</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>8.01985628102544</v>
+        <v>8.049066121263195</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>6.688747112752729</v>
+        <v>6.84866166376446</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>6.723125265108052</v>
+        <v>6.782295399884021</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>6.928756639579376</v>
+        <v>7.009802479546849</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>6.779022953135069</v>
+        <v>6.760715336580894</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.1402</t>
+          <t>X &gt; 0.1399</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4.175888703193451</v>
+        <v>4.127056316705939</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.783637521372235</v>
+        <v>4.903761237449785</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>5.424369095197079</v>
+        <v>5.5424716267162</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.590097197365317</v>
+        <v>6.704804045511999</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>6.347665632435309</v>
+        <v>6.510540155297548</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>7.23675563840176</v>
+        <v>7.225803550222672</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>8.631335219963987</v>
+        <v>8.640073714684526</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>8.460124564342934</v>
+        <v>8.616718830407379</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>8.695000395985836</v>
+        <v>8.874731472008044</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.69715260557313</v>
+        <v>7.903410265824327</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>6.604877482815901</v>
+        <v>6.814314066075859</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>6.935113623336896</v>
+        <v>7.167466054178206</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>7.698394722686217</v>
+        <v>7.952249130564233</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.74069842025002</v>
+        <v>7.021352989629747</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.1614</t>
+          <t>X &gt; 0.1611</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>4.321805057901017</v>
+        <v>4.342680053285612</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.921503318578694</v>
+        <v>4.95916455865428</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.057344178721614</v>
+        <v>6.088269209933493</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6.69777340394262</v>
+        <v>6.894972202078797</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>6.329551878057813</v>
+        <v>6.405723061126878</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>6.96706196211467</v>
+        <v>7.186122793143774</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>8.583031874957349</v>
+        <v>8.81751408124488</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>9.136371394435919</v>
+        <v>9.197705009524817</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>9.925729373967556</v>
+        <v>9.837551351318645</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>8.225470441583283</v>
+        <v>8.336903819573038</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>7.850701256112202</v>
+        <v>7.963558634304292</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>8.395283490100176</v>
+        <v>8.529339584867152</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>8.995540800052069</v>
+        <v>9.149410084699277</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>7.690664205380649</v>
+        <v>7.875612307120726</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.1826</t>
+          <t>X &gt; 0.1823</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>496</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>5.785213001723712</v>
+        <v>5.75601720737108</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>5.585317231240531</v>
+        <v>5.584130444795875</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.80344907229194</v>
+        <v>6.803295682287619</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7.941738732009327</v>
+        <v>7.941244239631324</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>6.798610469236223</v>
+        <v>6.847156389001995</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>8.104049015000349</v>
+        <v>8.128006423949962</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>9.632241881540622</v>
+        <v>9.680253560530943</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>10.17323775388291</v>
+        <v>10.22248531627663</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>10.91870721026336</v>
+        <v>10.99196432004306</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>10.27040131715931</v>
+        <v>10.36974864245389</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>10.46892596535073</v>
+        <v>10.56883400136941</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>11.71298153706089</v>
+        <v>11.83667815808914</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>12.09928229665071</v>
+        <v>12.24797184442854</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>10.10727601139337</v>
+        <v>10.27927477096004</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.2038</t>
+          <t>X &gt; 0.2035</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>5.752974184262783</v>
+        <v>5.585126270351118</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>4.619115060172703</v>
+        <v>4.47813966138574</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>6.849642004773266</v>
+        <v>6.703449292118655</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7.934521086309132</v>
+        <v>7.785714285714285</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>6.202914110779069</v>
+        <v>6.344084192381416</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.454942078361647</v>
+        <v>7.569250663581293</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>9.040876110503596</v>
+        <v>9.17526124102249</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>9.767124889151226</v>
+        <v>9.899904671115344</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>10.66079667057595</v>
+        <v>10.8153130143595</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>9.810877874246088</v>
+        <v>9.991484433544514</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>10.3221671694465</v>
+        <v>10.50162970029413</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>11.78852622872308</v>
+        <v>11.98836786623047</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>11.60703885989653</v>
+        <v>11.83130517776187</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>10.6394570876887</v>
+        <v>10.88987384930105</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.225</t>
+          <t>X &gt; 0.2246</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.233369683751363</v>
+        <v>5.324646009870847</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.622183590687534</v>
+        <v>3.741468924714994</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>6.941697920218211</v>
+        <v>7.051434640103999</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.500494492377996</v>
+        <v>8.605820105820101</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>6.247919224996593</v>
+        <v>6.407169255466471</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>7.688150397488826</v>
+        <v>7.819555913886539</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>9.317725752508366</v>
+        <v>9.1834012491625</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>9.99351425157878</v>
+        <v>9.857169628380298</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>11.07538923791313</v>
+        <v>10.95979815884464</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.6540418701547</v>
+        <v>9.566169008229096</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>10.59219785475166</v>
+        <v>10.50162970029413</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>10.34086172139269</v>
+        <v>10.27489615275875</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>11.06356801093644</v>
+        <v>11.01933936579606</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>10.14644651830582</v>
+        <v>10.12878308821029</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.2462</t>
+          <t>X &gt; 0.2458</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>301</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.33303745783774</v>
+        <v>3.303841663485109</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.386303192016442</v>
+        <v>2.385116405571786</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>4.98156502985276</v>
+        <v>4.981411639848439</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7.769597482411221</v>
+        <v>7.769102990033218</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>4.905726533966693</v>
+        <v>4.954272453732464</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.535326477223045</v>
+        <v>5.559283886172658</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>8.108423426926969</v>
+        <v>8.156435105917289</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>9.302484351246541</v>
+        <v>9.351731913640258</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>10.57040584920881</v>
+        <v>10.64366295898851</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>10.05271296650022</v>
+        <v>10.1520602917948</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.18023772186129</v>
+        <v>10.28014575787996</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>9.217938133352824</v>
+        <v>9.341634754381069</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>10.12669093452448</v>
+        <v>10.2753804823023</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>8.69129701664469</v>
+        <v>8.863295776211352</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.2674</t>
+          <t>X &gt; 0.267</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.251594257531487</v>
+        <v>1.998084896424494</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.640408164467658</v>
+        <v>0.4149078112686411</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>4.36086311716118</v>
+        <v>4.119530478691644</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6.960224063218682</v>
+        <v>6.708430913348934</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.187366608888425</v>
+        <v>5.399509641249473</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.484740638523512</v>
+        <v>5.262459094494638</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>5.811552913002195</v>
+        <v>5.611639070842941</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>8.6366653391743</v>
+        <v>8.834330900623549</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>10.6332963513758</v>
+        <v>10.84653861935559</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>10.1949001887908</v>
+        <v>10.43254610411438</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>9.990199030530604</v>
+        <v>9.818569591004518</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>9.201531915396224</v>
+        <v>9.05706419722187</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>10.01594896331737</v>
+        <v>9.891414467379356</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>7.361026177329919</v>
+        <v>7.271606870378335</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.2886</t>
+          <t>X &gt; 0.2882</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>196</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.110920704159525</v>
+        <v>2.081724909806894</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.093288910042837</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4052408552919928</v>
+        <v>-0.4053942452963142</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.296412859724938</v>
+        <v>3.295918367346935</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.717306980098634</v>
+        <v>0.7658528998644059</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.035089172999022</v>
+        <v>2.059046581948635</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.950378813732854</v>
+        <v>1.998390492723175</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>4.544534659742041</v>
+        <v>4.593782222135758</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.544776993015176</v>
+        <v>7.618034102794873</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>8.225470441583283</v>
+        <v>8.324817766877857</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.510565201690433</v>
+        <v>7.610473237709108</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.014331109147797</v>
+        <v>6.138027730176042</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>7.124792500732347</v>
+        <v>7.273482048510175</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.26889549789766</v>
+        <v>3.440894257464322</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.3098</t>
+          <t>X &gt; 0.3094</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1630352358323677</v>
+        <v>0.1214671224814339</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-3.760976295783607</v>
+        <v>-3.435394173200734</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.506741058022094</v>
+        <v>-1.197553214147007</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.259245674970238</v>
+        <v>3.537593984962406</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.07194949935799144</v>
+        <v>0.4167658966420689</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.693826840251354</v>
+        <v>2.005340889145195</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.9468648253560445</v>
+        <v>1.286790063077639</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.128802804085865</v>
+        <v>3.452536250062714</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>6.379078925708789</v>
+        <v>6.705037325136445</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>5.52916012937893</v>
+        <v>5.881208744321462</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>5.986710626747865</v>
+        <v>6.334963033627474</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>4.034333812215777</v>
+        <v>4.419445560466052</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>3.614182958902369</v>
+        <v>4.024287633902226</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.1335913246459342</v>
+        <v>0.3259640748649559</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.331</t>
+          <t>X &gt; 0.3306</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.990628684912799</v>
+        <v>1.522146239629144</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-2.059581798394923</v>
+        <v>-2.480385684236388</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.8283369229873614</v>
+        <v>-1.261220446744645</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4.179937001088796</v>
+        <v>3.707373271889402</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.236401332494694</v>
+        <v>-1.620585546481884</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.6869889573029937</v>
+        <v>0.2651031981434997</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.6022785980368255</v>
+        <v>0.2044471089180391</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.387242474575281</v>
+        <v>2.964420800147607</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>7.391300968459007</v>
+        <v>6.959706255526932</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>6.541382172129147</v>
+        <v>6.135877674711949</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>7.962697274031569</v>
+        <v>7.544640452982314</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.371059166224278</v>
+        <v>5.989903964540751</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>4.324892052748275</v>
+        <v>3.981842812170477</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.4855870525682988</v>
+        <v>0.1986296096697231</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.3522</t>
+          <t>X &gt; 0.3517</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>103</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.858889794708361</v>
+        <v>2.82969400035573</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-1.664917657578762</v>
+        <v>-1.666104444023418</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.088815255926036</v>
+        <v>-1.088968645930358</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3.895778819701157</v>
+        <v>3.895284327323154</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-2.467753451841133</v>
+        <v>-2.419207532075362</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.199505635798282</v>
+        <v>-1.175548226848669</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.28421599506445</v>
+        <v>-1.236204316074129</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.161336720372113</v>
+        <v>1.210584282765829</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>5.954723495888167</v>
+        <v>6.027980605667864</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>5.104804699558308</v>
+        <v>5.204152024852881</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>6.841851114113659</v>
+        <v>6.941759150132334</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.963607907245674</v>
+        <v>4.087304528273918</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>2.572583267524493</v>
+        <v>2.721272815302321</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-1.085176227880041</v>
+        <v>-0.9131774683133784</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.3734</t>
+          <t>X &gt; 0.3729</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.280988731370414</v>
+        <v>2.251792937017782</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-1.711149742645794</v>
+        <v>-1.71233652909045</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.2750312535515462</v>
+        <v>0.2748778635472249</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5.167161159044667</v>
+        <v>5.166666666666664</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-3.704461727384363</v>
+        <v>-3.655915807618591</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.634262568501313</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.3874381293736064</v>
+        <v>-0.3381905669798897</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>2.005789204835686</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>1.08261329872613</v>
+        <v>1.181960624020704</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>4.449340711894507</v>
+        <v>4.549248747913182</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.9122902928212611</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.6983367509683305</v>
+        <v>-0.5496472031905029</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-4.044029672170367</v>
+        <v>-3.872030912603705</v>
       </c>
     </row>
   </sheetData>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.423845874227553</v>
+        <v>9.394650079874921</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>6.622183590687527</v>
+        <v>6.620996804242871</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>8.608364586884875</v>
+        <v>8.608211196880553</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14.69097068285419</v>
+        <v>14.69047619047619</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>12.96220493928231</v>
+        <v>13.01075085904808</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.688150397488826</v>
+        <v>9.712107806438439</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>7.222487657270271</v>
+        <v>7.270499336260592</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.993514251578766</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.63889647637258</v>
+        <v>-1.565639366592883</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.679291463178622</v>
+        <v>-3.579944137884048</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-5.074468811915011</v>
+        <v>-4.974560775896336</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.659138278607308</v>
+        <v>-2.535441657579064</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-4.2697653223969</v>
+        <v>-4.121075774619072</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-4.044029672170367</v>
+        <v>-3.872030912603705</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>110</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.519083969465647</v>
+        <v>7.489888175113016</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>3.180625149129092</v>
+        <v>3.179438362684436</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.240399218919514</v>
+        <v>8.240245828915192</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>15.64335163523514</v>
+        <v>15.64285714285714</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>10.5596075366849</v>
+        <v>10.60815345645067</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>7.220617929956347</v>
+        <v>7.24457533890596</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>8.0449984797811</v>
+        <v>8.09301015877142</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.6038883458238331</v>
+        <v>-0.5546407834301164</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.573961411437509</v>
+        <v>-1.500704301657812</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.514789298676469</v>
+        <v>-1.415441973381895</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.628581366027561</v>
+        <v>-2.528673330008886</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.133069513600482</v>
+        <v>0.2567661346287267</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.105263157894747</v>
+        <v>-1.956573610116919</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.9704365985773009</v>
+        <v>-0.7984378390106386</v>
       </c>
     </row>
     <row r="8">
@@ -4015,1450 +4015,1450 @@
         <v>150</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>8.185750636132319</v>
+        <v>8.156554841779688</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>6.57456454306849</v>
+        <v>6.573377756623835</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.51312649164678</v>
+        <v>9.512973101642459</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>12.97668496856847</v>
+        <v>12.97619047619047</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>12.43839541547278</v>
+        <v>12.48694133523855</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.735769445107863</v>
+        <v>6.759726854057476</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6.651059085841695</v>
+        <v>6.699070764832015</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.183990442054963</v>
+        <v>2.23323800444868</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.7896749521988582</v>
+        <v>0.8629320619785545</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.273089489202327</v>
+        <v>1.372436814496901</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.401721664275463</v>
+        <v>2.501629700294139</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>4.436099816630794</v>
+        <v>4.559796437659038</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.682615629984042</v>
+        <v>4.83130517776187</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>4.908351280210574</v>
+        <v>5.080350039777237</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.1778</t>
+          <t>X &lt; -0.1779</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>207</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4.040823099900429</v>
+        <v>4.011627305547798</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.878912369155444</v>
+        <v>3.877725582710788</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.416508134158853</v>
+        <v>5.416354744154532</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.962192214945283</v>
+        <v>7.96169772256728</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>7.423902661849588</v>
+        <v>7.47244858161536</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.373450604528159</v>
+        <v>3.397408013477772</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3.288740245261991</v>
+        <v>3.336751924252312</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.372396239156409</v>
+        <v>1.421643801550125</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.311414082633632</v>
+        <v>1.384671192413329</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>1.910770648622616</v>
+        <v>2.01011797391719</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>1.222977702922812</v>
+        <v>1.322885738941487</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.189723005036583</v>
+        <v>3.313419626064828</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.218847514042025</v>
+        <v>4.367537061819853</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.961491376828938</v>
+        <v>4.133490136395601</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.1566</t>
+          <t>X &lt; -0.1567</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>282</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>3.902062692869897</v>
+        <v>3.872866898517266</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>5.482365961508201</v>
+        <v>5.481179175063545</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>7.215254151221245</v>
+        <v>7.215100761216924</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7.345479294809607</v>
+        <v>7.344984802431604</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.388750025401855</v>
+        <v>5.437295945167627</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.913074409646875</v>
+        <v>3.937031818596488</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3.119144192224681</v>
+        <v>3.167155871215002</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.94285569028191</v>
+        <v>1.992103252675626</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.527263604681124</v>
+        <v>1.600520714460821</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>2.095784524663316</v>
+        <v>2.195131849957889</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.245693295481139</v>
+        <v>2.345601331499815</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>4.05312109322653</v>
+        <v>4.176817714254774</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>4.696800027147169</v>
+        <v>4.845489574924997</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>5.63175553552972</v>
+        <v>5.449144366018373</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.1354</t>
+          <t>X &lt; -0.1355</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.505606880516865</v>
+        <v>2.476411086164234</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.207089251064893</v>
+        <v>5.205902464620237</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.69911031914004</v>
+        <v>6.698956929135718</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6.559793683752659</v>
+        <v>6.559299191374656</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>6.560587688608457</v>
+        <v>6.609133608374229</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3.89300214951038</v>
+        <v>3.916959558459993</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>2.191041116389769</v>
+        <v>2.23905279538009</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.802139588505995</v>
+        <v>2.851387150899711</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.010699210958961</v>
+        <v>3.083956320738658</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.621696856677609</v>
+        <v>1.721044181972182</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.147453919441688</v>
+        <v>1.247361955460363</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.799082745651454</v>
+        <v>2.922779366679698</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.187557229265266</v>
+        <v>3.336246777043094</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.575017946877246</v>
+        <v>3.315749860082718</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.1142</t>
+          <t>X &lt; -0.1143</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.810501135134309</v>
+        <v>1.781305340781678</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5.189335002150322</v>
+        <v>5.188148215705667</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.592966811008054</v>
+        <v>5.592813421003733</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.72119594661239</v>
+        <v>6.720701454234387</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>6.981309587129473</v>
+        <v>7.029855506895245</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>5.482276431135809</v>
+        <v>5.506233840085422</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.800759684644099</v>
+        <v>3.84877136363442</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.132094234470131</v>
+        <v>4.181341796863848</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.073108085931381</v>
+        <v>3.146365195711077</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.225185297585561</v>
+        <v>1.324532622880135</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>1.220084937728558</v>
+        <v>1.319992973747233</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.169433149964121</v>
+        <v>2.176562904724896</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.066717166390198</v>
+        <v>1.981005776564274</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.807949673784876</v>
+        <v>1.431647444966863</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.09304</t>
+          <t>X &lt; -0.09312</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.05525092881291016</v>
+        <v>0.1461381751130233</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.306958909265667</v>
+        <v>1.375461089957163</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.694660137969159</v>
+        <v>1.919223101642459</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2.450863372324342</v>
+        <v>2.674107142857139</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>4.10349713691253</v>
+        <v>4.372358001905219</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.583969758096913</v>
+        <v>1.764421689738235</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.06568582808631618</v>
+        <v>0.1388203735957134</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.6892489945647569</v>
+        <v>-0.5546407834301164</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.750231151087533</v>
+        <v>-0.5916133925669129</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.226128038184214</v>
+        <v>-2.042401221030786</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-2.346449704585552</v>
+        <v>-2.246541668566877</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.227427132610451</v>
+        <v>-2.188374931201984</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.248201980078846</v>
+        <v>-2.270053233941361</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.936793076744806</v>
+        <v>-2.177748183838226</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.07184</t>
+          <t>X &lt; -0.07193</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.875977758929416</v>
+        <v>-0.8455002342581324</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.129139160635212</v>
+        <v>-1.07232713445714</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.030083384896436</v>
+        <v>-0.7262377491590257</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.7764014511846185</v>
+        <v>-0.4730491456755317</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.401358378435745</v>
+        <v>1.503792958748626</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4000330240279339</v>
+        <v>-0.3760756150783209</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-2.089681654899046</v>
+        <v>-2.100269985064976</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.309836718438874</v>
+        <v>-2.37732305165693</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-2.864646035455465</v>
+        <v>-2.90934516574422</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-3.83802162190878</v>
+        <v>-3.856936122796832</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.22538999621073</v>
+        <v>-4.184838946570544</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-3.012745067857658</v>
+        <v>-3.012810823067035</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.862613614129955</v>
+        <v>-3.903018254581355</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-3.695453517142603</v>
+        <v>-3.901498145041238</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.05064</t>
+          <t>X &lt; -0.05075</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.7231035305343525</v>
+        <v>-0.7122498229433418</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.553039623598181</v>
+        <v>-1.61515479925567</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.94781100835322</v>
+        <v>-1.814529327900786</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.133992114764858</v>
+        <v>-0.9071914480077723</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3050941678605525</v>
+        <v>-0.177131297705678</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.5936576382254657</v>
+        <v>-0.3379686993342688</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-2.240867997491634</v>
+        <v>-2.002683621132896</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.438405391278373</v>
+        <v>-1.246436792299285</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.694700047801149</v>
+        <v>-1.523786688021453</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.078816669155451</v>
+        <v>-2.979469343860877</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-3.427371616872612</v>
+        <v>-3.425310938975265</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-3.145356272171036</v>
+        <v>-3.17144948536771</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.003658879819874</v>
+        <v>-4.055844202538196</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.118799521228738</v>
+        <v>-4.296036131129476</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.02944</t>
+          <t>X &lt; -0.02956</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.6206274959861346</v>
+        <v>-0.6161724309475929</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.168791569308134</v>
+        <v>-1.062985879739806</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.563562954063173</v>
+        <v>-1.380966292296939</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.281477521940253</v>
+        <v>-1.023809523809526</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.002556387378625402</v>
+        <v>0.1953062581599525</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4593710256590313</v>
+        <v>-0.2488720331453536</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.986754126003405</v>
+        <v>-1.710952014211266</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.542661038582857</v>
+        <v>-1.300703231620211</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.983293916442001</v>
+        <v>-1.753037519770501</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.564803114647731</v>
+        <v>-2.536238984589858</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.348595192505272</v>
+        <v>-2.395044582518757</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-2.577598813506199</v>
+        <v>-2.641523694354163</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.490017017896122</v>
+        <v>-3.569811857018522</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-3.299982053122754</v>
+        <v>-3.320766995003154</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.008234</t>
+          <t>X &lt; -0.00838</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1671</v>
+        <v>1677</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-1.408210428627321</v>
+        <v>-1.294936958259839</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.410338118830595</v>
+        <v>-1.364937783115195</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.328351458293625</v>
+        <v>-1.252605533372382</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.376910581689771</v>
+        <v>-1.269256871394646</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.7828997772169259</v>
+        <v>-0.7168613979759471</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.200662815519863</v>
+        <v>-1.06587758510225</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-2.267247413860147</v>
+        <v>-2.106005578614344</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-2.376534304516298</v>
+        <v>-2.242952471741795</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.644692589567256</v>
+        <v>-2.546240064287083</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.105019963533998</v>
+        <v>-3.040753491422848</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-2.919664237755597</v>
+        <v>-2.915186042103002</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.331582988708924</v>
+        <v>-3.334061642245558</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.421052631578945</v>
+        <v>-3.431068107867226</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-3.582372837084449</v>
+        <v>-3.659065583359315</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.01297</t>
+          <t>X &lt; 0.0128</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.608823007278538</v>
+        <v>-1.470962477376112</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-2.008768790264845</v>
+        <v>-1.868917536735296</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.306640950213684</v>
+        <v>-2.140631155735385</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.829745795690698</v>
+        <v>-2.614645277278385</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.010788620720469</v>
+        <v>-1.868183765649256</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-2.343564857687412</v>
+        <v>-2.199575471523907</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.033389669412102</v>
+        <v>-2.864994512272524</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.135757253238587</v>
+        <v>-3.014741303666419</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.928771649742892</v>
+        <v>-2.832361484843382</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.170491537185896</v>
+        <v>-3.145362538253906</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.863584458173513</v>
+        <v>-2.838179268460912</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-2.803245508276028</v>
+        <v>-2.802691414624739</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.856943384283142</v>
+        <v>-2.857713286766796</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-3.140310520276039</v>
+        <v>-3.191758803760173</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.03417</t>
+          <t>X &lt; 0.03399</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2436</v>
+        <v>2440</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.234491837645102</v>
+        <v>-1.185203549306067</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.96618225442402</v>
+        <v>-1.931788094382149</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.80793690303625</v>
+        <v>-1.77384860378389</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.024406138905611</v>
+        <v>-1.989795918367356</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.662532025880189</v>
+        <v>-1.641002043011078</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.733406768749191</v>
+        <v>-1.673279681890229</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-2.123944325264866</v>
+        <v>-2.080114632252851</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.405690147625627</v>
+        <v>-2.360929343602571</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.789595838460713</v>
+        <v>-1.721935013686078</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.125817614622818</v>
+        <v>-2.073826142404357</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.021402566966849</v>
+        <v>-1.969375893920621</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.841723535843919</v>
+        <v>-1.848065970203372</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.870249915085026</v>
+        <v>-1.893261256759494</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-2.073586322416681</v>
+        <v>-2.113639031261009</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.05537</t>
+          <t>X &lt; 0.05517</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2738</v>
+        <v>2746</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.9900069396252675</v>
+        <v>-1.005943648011311</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.454779460811714</v>
+        <v>-1.482701527881851</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.57566535697039</v>
+        <v>-1.603457801513144</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.608195507101946</v>
+        <v>-1.599523118391048</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.236401332494694</v>
+        <v>-1.234776753085711</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.137986320854743</v>
+        <v>-1.124078519943978</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.713239639112757</v>
+        <v>-1.673855739587403</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.833016360666129</v>
+        <v>-1.793409282373027</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.582909809011504</v>
+        <v>-1.556551762085434</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.574467038879369</v>
+        <v>-1.560896518836429</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.467425848797625</v>
+        <v>-1.45423303767118</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.486041302590621</v>
+        <v>-1.485327288687401</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.375069656616901</v>
+        <v>-1.387357605880887</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.530898780661104</v>
+        <v>-1.555241123126372</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.07657</t>
+          <t>X &lt; 0.07635</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3003</v>
+        <v>3013</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.9888735902160519</v>
+        <v>-0.9569062730033124</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.256281228075792</v>
+        <v>-1.233784777811429</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.533986978824359</v>
+        <v>-1.510836422167067</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.518945079003167</v>
+        <v>-1.495746892868958</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.309280547342631</v>
+        <v>-1.305690475924031</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.126956116720983</v>
+        <v>-1.114486982420509</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.659018433538151</v>
+        <v>-1.654130118170187</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-1.77612919902181</v>
+        <v>-1.771178468997277</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.586654835035191</v>
+        <v>-1.591673637159957</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.52083579624275</v>
+        <v>-1.535971096231194</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.441259040980682</v>
+        <v>-1.456814154701433</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.555026084644858</v>
+        <v>-1.579507044928029</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.590797596824657</v>
+        <v>-1.624788606799065</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.679727307868006</v>
+        <v>-1.722614889971616</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.09777</t>
+          <t>X &lt; 0.09754</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3209</v>
+        <v>3217</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-1.053231362626214</v>
+        <v>-1.024043713431873</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.468693244368133</v>
+        <v>-1.445410309857024</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.72289835307371</v>
+        <v>-1.667943874813552</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-1.824806177750261</v>
+        <v>-1.800588782150605</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.538816103068754</v>
+        <v>-1.498592866042706</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.318110981790902</v>
+        <v>-1.302288649818486</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.728294147989146</v>
+        <v>-1.687612444431828</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.681224695321923</v>
+        <v>-1.640585555381712</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.632229217060633</v>
+        <v>-1.598892891466512</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.718507149453139</v>
+        <v>-1.692035916539012</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-1.470424454445997</v>
+        <v>-1.444540071962585</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.574696404691743</v>
+        <v>-1.58683295034966</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.603988731386664</v>
+        <v>-1.623221443327829</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-1.641560426447775</v>
+        <v>-1.667966196882176</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.119</t>
+          <t>X &lt; 0.1187</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3366</v>
+        <v>3373</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.95679646853376</v>
+        <v>-0.974376443906479</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.250183828749158</v>
+        <v>-1.27201859985081</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-1.570083458012682</v>
+        <v>-1.620596638310261</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-1.720392440594239</v>
+        <v>-1.770681136776318</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.531974954897585</v>
+        <v>-1.564310389579106</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.604084338729315</v>
+        <v>-1.630690182322283</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.850966806044852</v>
+        <v>-1.882783278560488</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.768559973128909</v>
+        <v>-1.800302490766867</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.754377257827848</v>
+        <v>-1.791893278459582</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.727899630481154</v>
+        <v>-1.741174872404699</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.411872874163237</v>
+        <v>-1.455321326562093</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.420590603005003</v>
+        <v>-1.440203562340969</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.468062520694104</v>
+        <v>-1.49313663215711</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.463603562332494</v>
+        <v>-1.464960761685354</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.1402</t>
+          <t>X &lt; 0.1399</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3489</v>
+        <v>3498</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7961644600032258</v>
+        <v>-0.7869560288174853</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.7930447114302339</v>
+        <v>-0.8169356336895675</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.9725877940675076</v>
+        <v>-0.9960038148579713</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.17002361483631</v>
+        <v>-1.192946733995768</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.121353012200174</v>
+        <v>-1.1537772276357</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-1.266136950850573</v>
+        <v>-1.264992674369971</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-1.507217039253646</v>
+        <v>-1.510154151953522</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-1.501274221750478</v>
+        <v>-1.53274373071114</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.518281544652893</v>
+        <v>-1.554424489548722</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.32219632051234</v>
+        <v>-1.363523589082007</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.110305827133466</v>
+        <v>-1.15218349593551</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.174708929669222</v>
+        <v>-1.221155943293354</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.321204809366471</v>
+        <v>-1.371991002099037</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.16559540938529</v>
+        <v>-1.22153675267559</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.1614</t>
+          <t>X &lt; 0.1611</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3577</v>
+        <v>3585</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.6981862255204234</v>
+        <v>-0.7035526253316675</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.6788951021437342</v>
+        <v>-0.6876731191059449</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.9194264626453048</v>
+        <v>-0.927516331060545</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.9972951448038856</v>
+        <v>-1.033081661037166</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.9350940807161052</v>
+        <v>-0.9510108072211025</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-1.013184529787523</v>
+        <v>-1.05287171723856</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.250354604634495</v>
+        <v>-1.293505330193966</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-1.367595752009606</v>
+        <v>-1.382467927046726</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-1.469398191296406</v>
+        <v>-1.460187715180226</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.187303324723018</v>
+        <v>-1.210269603261061</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.125280197921931</v>
+        <v>-1.148314558345774</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.215199428968539</v>
+        <v>-1.242080711304816</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.312539950414681</v>
+        <v>-1.343076677601573</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.127246520553562</v>
+        <v>-1.162327784490536</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.1826</t>
+          <t>X &lt; 0.1823</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3669</v>
+        <v>3680</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.7698894145647728</v>
+        <v>-0.7635643025474224</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.6283694422615866</v>
+        <v>-0.6263333304111995</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.8455691605271269</v>
+        <v>-0.8430279820746875</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.9725766061348011</v>
+        <v>-0.9696089818041074</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.8166344920856758</v>
+        <v>-0.8209108378887677</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.9668867057397463</v>
+        <v>-0.9673158068246579</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-1.1458215815504</v>
+        <v>-1.149044233811857</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-1.244580986516475</v>
+        <v>-1.247680787376247</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.318109478938872</v>
+        <v>-1.324313528252112</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.227681905661093</v>
+        <v>-1.237769483005813</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.254051756203836</v>
+        <v>-1.264140957683956</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.422612614132852</v>
+        <v>-1.435495975884329</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.473605986728032</v>
+        <v>-1.489803216696153</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-1.23283160340894</v>
+        <v>-1.252983293556085</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.2038</t>
+          <t>X &lt; 0.2035</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3746</v>
+        <v>3756</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.6320200475601538</v>
+        <v>-0.6130569031570801</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3933261789467721</v>
+        <v>-0.3777899716139643</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.693953625467941</v>
+        <v>-0.677629499897229</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.7890232316445136</v>
+        <v>-0.7724375995751487</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.5940058273146107</v>
+        <v>-0.6100042158902639</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.7083790187529075</v>
+        <v>-0.7213216758752097</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.8586664670493178</v>
+        <v>-0.87396493363552</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.9649079232613147</v>
+        <v>-0.9799464718936974</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.038104306665446</v>
+        <v>-1.055706597952316</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.9402438441310039</v>
+        <v>-0.960896518836428</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.9968735166616725</v>
+        <v>-1.01739131593358</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.161196519192764</v>
+        <v>-1.184038935766552</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.139642176260949</v>
+        <v>-1.165323337897782</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.059258614788533</v>
+        <v>-1.087914070978883</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.225</t>
+          <t>X &lt; 0.2246</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3815</v>
+        <v>3825</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.4694217776607914</v>
+        <v>-0.4778033308796878</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.2117781100105134</v>
+        <v>-0.2230778076190632</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.5663298596339317</v>
+        <v>-0.5767036449685961</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.6834457503857649</v>
+        <v>-0.6935183460607206</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.4754818509149459</v>
+        <v>-0.4906277831756327</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5823925568103405</v>
+        <v>-0.5949996438988663</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.7052988419448027</v>
+        <v>-0.6937615246599762</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7918448541153325</v>
+        <v>-0.7800744466084879</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.8647753095812476</v>
+        <v>-0.8550836038177962</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.7316237865243025</v>
+        <v>-0.7245423793744408</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.8170665319878481</v>
+        <v>-0.8097600593714773</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.7943604051839017</v>
+        <v>-0.7893891733504645</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.8593130911899536</v>
+        <v>-0.8564453014156825</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.8024394581030876</v>
+        <v>-0.8020029013992271</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.2462</t>
+          <t>X &lt; 0.2458</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3864</v>
+        <v>3875</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.2498095048701785</v>
+        <v>-0.2467373392902843</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.06733432174059573</v>
+        <v>-0.06704759283161366</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.3191315728693525</v>
+        <v>-0.3182157815279041</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5104945186110115</v>
+        <v>-0.5090090090090129</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2861075538016848</v>
+        <v>-0.2892344285788155</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.3103738055808307</v>
+        <v>-0.3114380528014777</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.4843925631723422</v>
+        <v>-0.4869158400108518</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.6015392737073171</v>
+        <v>-0.6038314793613395</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.6742692194217241</v>
+        <v>-0.6783050514235214</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.6310814863233603</v>
+        <v>-0.6373595247658059</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.6404298743849992</v>
+        <v>-0.6467285599774826</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.5657970621414137</v>
+        <v>-0.5742419081409835</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.635193770619658</v>
+        <v>-0.6454750079966445</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.5502408522945927</v>
+        <v>-0.5626607129109331</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.2674</t>
+          <t>X &lt; 0.267</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3922</v>
+        <v>3932</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.1302171741175755</v>
+        <v>-0.1146745625295722</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.07668282810491434</v>
+        <v>0.09028106967318905</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.2026121302703316</v>
+        <v>-0.1882696069550533</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.3383370728014867</v>
+        <v>-0.3236573168080028</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.226914514146479</v>
+        <v>-0.240961904209982</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.2209735574366647</v>
+        <v>-0.2081242457733126</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.2154888059034406</v>
+        <v>-0.2042041780468864</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.4141086753924341</v>
+        <v>-0.4276727793671355</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.5120821142640963</v>
+        <v>-0.5269587178030122</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.4820472063317283</v>
+        <v>-0.4984981448527037</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.4687666584421564</v>
+        <v>-0.4598273094474905</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.420169296519056</v>
+        <v>-0.4129200510716871</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.4692239485697769</v>
+        <v>-0.4633808125762826</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.3311523743874147</v>
+        <v>-0.3272457554075672</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.2886</t>
+          <t>X &lt; 0.2882</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3969</v>
+        <v>3980</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.09518021938416865</v>
+        <v>-0.09338254865357243</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.3163379668313624</v>
+        <v>0.3155287252277077</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.08599081325481706</v>
+        <v>0.08576187638563226</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.07165213455626684</v>
+        <v>-0.0714285714285765</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.05729938731793283</v>
+        <v>0.05458569054898987</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.01646678816376834</v>
+        <v>0.01515981962083401</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.04609597383633712</v>
+        <v>0.04343996473169653</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.1053177340456699</v>
+        <v>-0.1076216710823488</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.2279395420135231</v>
+        <v>-0.2311708238432786</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2585826309419872</v>
+        <v>-0.2631053541777959</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.2226489298836398</v>
+        <v>-0.227301591027306</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.1489753113806245</v>
+        <v>-0.1550872054014079</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.202354982946261</v>
+        <v>-0.2096393085481054</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.03798280898065087</v>
+        <v>-0.0469531428023231</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.3098</t>
+          <t>X &lt; 0.3094</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4014</v>
+        <v>4024</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.01473830271621068</v>
+        <v>0.004131425051092208</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.2546440264266607</v>
+        <v>0.2426873040305111</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.1218221438206939</v>
+        <v>0.1102469554218857</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.03259269876087956</v>
+        <v>-0.04380621857072242</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.08890498544543846</v>
+        <v>0.07550237334087484</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.05186425697593222</v>
+        <v>0.03948875881938108</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1050920792927457</v>
+        <v>0.09161190433420785</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-8.915993508651354e-05</v>
+        <v>-0.01324669364892372</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.09711280594994065</v>
+        <v>-0.1110068806871212</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.06223488444957326</v>
+        <v>-0.0770832119844016</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.07873638899811652</v>
+        <v>-0.09351970786743635</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.00546724844225821</v>
+        <v>-0.02142561897286299</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.01179786327587351</v>
+        <v>-0.005133745633564502</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.1270857097073375</v>
+        <v>0.1088457322888416</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.331</t>
+          <t>X &lt; 0.3306</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4042</v>
+        <v>4052</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.05181615383891369</v>
+        <v>-0.03778710163975063</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1752881082715803</v>
+        <v>0.1882071529492961</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.08998314104228911</v>
+        <v>0.1031773841922927</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.03779347828904633</v>
+        <v>-0.02430189210100764</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.1285130818925921</v>
+        <v>0.1400645397037863</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.09379413646589541</v>
+        <v>0.1061964763891723</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.1213809760203475</v>
+        <v>0.1329214669754109</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.01370058698249466</v>
+        <v>0.02558234484624222</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.08307029119131215</v>
+        <v>-0.07174873664112624</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.05431205965250285</v>
+        <v>-0.04373675552282918</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.09683622612420351</v>
+        <v>-0.08612204652049371</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.04856882827524345</v>
+        <v>-0.03878932126220036</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.01512449303952934</v>
+        <v>0.02400194558816793</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.1064380359420696</v>
+        <v>0.1142427676482569</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.3522</t>
+          <t>X &lt; 0.3517</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4062</v>
+        <v>4073</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.06373811642392724</v>
+        <v>-0.06273052288012337</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1543387207808067</v>
+        <v>0.1539571119889871</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.09206093800082016</v>
+        <v>0.09181737196566786</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.009890015059554003</v>
+        <v>-0.009849200517834333</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.1529618610635382</v>
+        <v>0.1511582223853694</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.1444508537892801</v>
+        <v>0.1433746527996149</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1714981781657769</v>
+        <v>0.1696590001261455</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.08664530931159931</v>
+        <v>0.08499905699424204</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.009931637424948292</v>
+        <v>-0.01200663346038766</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.01452251100917579</v>
+        <v>0.01163230137450455</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.02878264076758086</v>
+        <v>-0.03157278580334122</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.04403944917672931</v>
+        <v>0.04036903479605058</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.08076149921040354</v>
+        <v>0.07627326809078738</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.1481346381623325</v>
+        <v>0.1427937749437831</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.3734</t>
+          <t>X &lt; 0.3729</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4081</v>
+        <v>4092</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.03831710527787635</v>
+        <v>-0.03751742781025058</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.1468424158594317</v>
+        <v>0.1464771718285078</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.05858103710131957</v>
+        <v>0.05842764709699821</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.01785589348644123</v>
+        <v>-0.01779619697708767</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.1661867765159784</v>
+        <v>0.1645809353360903</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2080120472110707</v>
+        <v>0.2068813256021969</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.2345554981052373</v>
+        <v>0.2327781731429894</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.123473355357298</v>
+        <v>0.1219642123549747</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.1004923775537279</v>
+        <v>0.09847026066051257</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.1209067066645773</v>
+        <v>0.1182050436635649</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.05239094276060996</v>
+        <v>0.04985924852368839</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.1250540169736709</v>
+        <v>0.121757030396374</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1596693618148493</v>
+        <v>0.1556801268619665</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.203295329871608</v>
+        <v>0.1986296096697231</v>
       </c>
     </row>
   </sheetData>
